--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G553"/>
+  <dimension ref="A1:G556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14469,6 +14469,81 @@
       </c>
       <c r="G553" t="inlineStr"/>
     </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Dětská postel se zábranou BASIC GUARD vč. roštu</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>T.ROZOWE 1/3</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>21</v>
+      </c>
+      <c r="D554" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E554" t="n">
+        <v>95</v>
+      </c>
+      <c r="F554" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Dětská postel se zábranou BASIC GUARD vč. roštu</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>T.ROZOWE 2/3</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>30</v>
+      </c>
+      <c r="D555" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E555" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F555" t="n">
+        <v>1</v>
+      </c>
+      <c r="G555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Dětská postel se zábranou BASIC GUARD vč. roštu</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>T.ROZOWE 3/3</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>2</v>
+      </c>
+      <c r="D556" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E556" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G556" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G556"/>
+  <dimension ref="A1:G558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14544,6 +14544,56 @@
       </c>
       <c r="G556" t="inlineStr"/>
     </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Psací stůl PALIEND grafit</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>PALIEND 1/2</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D557" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E557" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F557" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Psací stůl PALIEND grafit</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>PALIEND 2/2</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D558" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E558" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F558" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G558" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G558"/>
+  <dimension ref="A1:G559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14594,6 +14594,31 @@
       </c>
       <c r="G558" t="inlineStr"/>
     </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Sendvičová matrace OLIVER výška 11 cm</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>PALIEND</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>10</v>
+      </c>
+      <c r="D559" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E559" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G559" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G559"/>
+  <dimension ref="A1:G560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14619,6 +14619,31 @@
       </c>
       <c r="G559" t="inlineStr"/>
     </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Laťkový rošt s textilií 12 latí  MASIV</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>PALIEND</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>6</v>
+      </c>
+      <c r="D560" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E560" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F560" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G560" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G560"/>
+  <dimension ref="A1:G563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14644,6 +14644,81 @@
       </c>
       <c r="G560" t="inlineStr"/>
     </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 200x200 masiv borovice - VMK2A</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>VMK2A-200 1/3</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>8</v>
+      </c>
+      <c r="D561" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E561" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F561" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 200x200 masiv borovice - VMK2A</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>VMK2A-200 2/3</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>12</v>
+      </c>
+      <c r="D562" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E562" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F562" t="n">
+        <v>2</v>
+      </c>
+      <c r="G562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 200x200 masiv borovice - VMK2A</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>VMK2A-200 3/3</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>10</v>
+      </c>
+      <c r="D563" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E563" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F563" t="n">
+        <v>1</v>
+      </c>
+      <c r="G563" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -14627,7 +14627,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>PALIEND</t>
+          <t>ROST12</t>
         </is>
       </c>
       <c r="C560" t="n">

--- a/products.xlsx
+++ b/products.xlsx
@@ -14487,7 +14487,7 @@
         <v>0.1</v>
       </c>
       <c r="E554" t="n">
-        <v>95</v>
+        <v>0.95</v>
       </c>
       <c r="F554" t="n">
         <v>2.05</v>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G563"/>
+  <dimension ref="A1:G566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14719,6 +14719,81 @@
       </c>
       <c r="G563" t="inlineStr"/>
     </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Patrová postel PP06, se zábranou  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>LP06 1/3</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>19</v>
+      </c>
+      <c r="D564" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E564" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F564" t="n">
+        <v>1</v>
+      </c>
+      <c r="G564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Patrová postel PP06, se zábranou  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>LP06 2/3</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>27</v>
+      </c>
+      <c r="D565" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E565" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F565" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Patrová postel PP06, se zábranou  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>LP06 3/3</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>24</v>
+      </c>
+      <c r="D566" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E566" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F566" t="n">
+        <v>1</v>
+      </c>
+      <c r="G566" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G566"/>
+  <dimension ref="A1:G568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14794,6 +14794,56 @@
       </c>
       <c r="G566" t="inlineStr"/>
     </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Patrová postel ZP04, vyvýšené patro</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>ZP04 1/2</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>24</v>
+      </c>
+      <c r="D567" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E567" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F567" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Patrová postel ZP04, vyvýšené patro</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>ZP04 2/2</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>22</v>
+      </c>
+      <c r="D568" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E568" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F568" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G568" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G568"/>
+  <dimension ref="A1:G572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14844,6 +14844,106 @@
       </c>
       <c r="G568" t="inlineStr"/>
     </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Obývací stěna TERA | ŠEDÝ BETON / BÍLÁ</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>STĚNA-TERA 1/4</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>18</v>
+      </c>
+      <c r="D569" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E569" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F569" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Obývací stěna TERA | ŠEDÝ BETON / BÍLÁ</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>STĚNA-TERA 2/4</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>8</v>
+      </c>
+      <c r="D570" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E570" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F570" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Obývací stěna TERA | ŠEDÝ BETON / BÍLÁ</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>STĚNA-TERA 3/4</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>23</v>
+      </c>
+      <c r="D571" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E571" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F571" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Obývací stěna TERA | ŠEDÝ BETON / BÍLÁ</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>STĚNA-TERA 4/4</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>16</v>
+      </c>
+      <c r="D572" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E572" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F572" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G572" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G572"/>
+  <dimension ref="A1:G573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14944,6 +14944,31 @@
       </c>
       <c r="G572" t="inlineStr"/>
     </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Dětský povlak na polštář TROLLOVÉ</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>POVLAK</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>5</v>
+      </c>
+      <c r="D573" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E573" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F573" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G573" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G573"/>
+  <dimension ref="A1:G574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14969,6 +14969,31 @@
       </c>
       <c r="G573" t="inlineStr"/>
     </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Pěnová matrace výška 9 cm KIDS COCO</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>MAT-KIDS-COCO</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>5</v>
+      </c>
+      <c r="D574" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E574" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F574" t="n">
+        <v>2</v>
+      </c>
+      <c r="G574" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G574"/>
+  <dimension ref="A1:G575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14994,6 +14994,31 @@
       </c>
       <c r="G574" t="inlineStr"/>
     </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Dětská rostoucí otočná židle s podnoží a šlemi JOAN</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>ŽIDLE-JOAN</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>9</v>
+      </c>
+      <c r="D575" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E575" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F575" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G575" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G575"/>
+  <dimension ref="A1:G576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15019,6 +15019,31 @@
       </c>
       <c r="G575" t="inlineStr"/>
     </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Pěnová matrace výška 10 cm EUREKA PUR</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>MAT-EUREKA</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>8</v>
+      </c>
+      <c r="D576" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E576" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F576" t="n">
+        <v>2</v>
+      </c>
+      <c r="G576" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G576"/>
+  <dimension ref="A1:G577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15044,6 +15044,31 @@
       </c>
       <c r="G576" t="inlineStr"/>
     </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Dětská matrace JUNIOR COCO Aloe Vera 11 cm – kokosová pěnová matrace PUR T25 H3, nosnost 60 kg</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>MAT-JUNIOR-COCO</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>8</v>
+      </c>
+      <c r="D577" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E577" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F577" t="n">
+        <v>2</v>
+      </c>
+      <c r="G577" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G577"/>
+  <dimension ref="A1:G579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15069,6 +15069,56 @@
       </c>
       <c r="G577" t="inlineStr"/>
     </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Dětská postel ANNITTI PINE se zábranou včetně roštu a zásuvek</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>ANNITTI-PINE 1/2</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>20</v>
+      </c>
+      <c r="D578" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E578" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F578" t="n">
+        <v>1</v>
+      </c>
+      <c r="G578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Dětská postel ANNITTI PINE se zábranou včetně roštu a zásuvek</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>ANNITTI-PINE 2/2</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>30</v>
+      </c>
+      <c r="D579" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E579" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F579" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G579" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G579"/>
+  <dimension ref="A1:G581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15119,6 +15119,56 @@
       </c>
       <c r="G579" t="inlineStr"/>
     </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Dětská postel MOCHUMA se zábranou proti pádu 120x200, 140x200, 160x200 cm s roštem</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>MOCHUMA 1/2</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>21</v>
+      </c>
+      <c r="D580" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E580" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F580" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Dětská postel MOCHUMA se zábranou proti pádu 120x200, 140x200, 160x200 cm s roštem</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>MOCHUMA 2/2</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>35</v>
+      </c>
+      <c r="D581" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E581" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F581" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G581" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G581"/>
+  <dimension ref="A1:G584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15169,6 +15169,81 @@
       </c>
       <c r="G581" t="inlineStr"/>
     </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Patrová postel KARMA KIDBED THREE + rošty  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>KARMA-KIDBED-THREE 1/3</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>30</v>
+      </c>
+      <c r="D582" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E582" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F582" t="n">
+        <v>1</v>
+      </c>
+      <c r="G582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Patrová postel KARMA KIDBED THREE + rošty  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>KARMA-KIDBED-THREE 2/3</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>27</v>
+      </c>
+      <c r="D583" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E583" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F583" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Patrová postel KARMA KIDBED THREE + rošty  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>KARMA-KIDBED-THREE 3/3</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>16</v>
+      </c>
+      <c r="D584" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E584" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F584" t="n">
+        <v>1</v>
+      </c>
+      <c r="G584" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G584"/>
+  <dimension ref="A1:G586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15244,6 +15244,56 @@
       </c>
       <c r="G584" t="inlineStr"/>
     </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Rohová lavice CEZAR</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>CEZAR 1/2</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D585" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E585" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F585" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Rohová lavice CEZAR</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>CEZAR 2/2</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>7</v>
+      </c>
+      <c r="D586" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E586" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F586" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G586" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G586"/>
+  <dimension ref="A1:G588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15294,6 +15294,56 @@
       </c>
       <c r="G586" t="inlineStr"/>
     </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Psací stůl ERIDAN</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>ERIDAN 1/2</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>25</v>
+      </c>
+      <c r="D587" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E587" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F587" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Psací stůl ERIDAN</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>ERIDAN 2/2</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D588" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E588" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F588" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G588" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G588"/>
+  <dimension ref="A1:G589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15344,6 +15344,31 @@
       </c>
       <c r="G588" t="inlineStr"/>
     </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Toaletní stolek DRESS-03</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>DRESS-03</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D589" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E589" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F589" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G589" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G589"/>
+  <dimension ref="A1:G592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15369,6 +15369,81 @@
       </c>
       <c r="G589" t="inlineStr"/>
     </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 140x200 masiv borovice - VMK14A</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>VMK14A-140 1/3</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>18</v>
+      </c>
+      <c r="D590" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E590" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F590" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 140x200 masiv borovice - VMK14A</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>VMK14A-140 2/3</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>8</v>
+      </c>
+      <c r="D591" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E591" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F591" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 140x200 masiv borovice - VMK14A</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>VMK14A-140 3/3</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>12</v>
+      </c>
+      <c r="D592" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E592" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F592" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G592" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G592"/>
+  <dimension ref="A1:H594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>ZBOZI_OBAL</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ZBOZI_TYP_DOPRAVCE</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -481,6 +486,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -510,6 +520,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -539,6 +554,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -568,6 +588,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -597,6 +622,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -626,6 +656,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -655,6 +690,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -684,6 +724,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -713,6 +758,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -742,6 +792,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -771,6 +826,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -800,6 +860,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -829,6 +894,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -858,6 +928,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -887,6 +962,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -916,6 +996,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -945,6 +1030,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -974,6 +1064,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1003,6 +1098,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1032,6 +1132,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1061,6 +1166,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1090,6 +1200,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1119,6 +1234,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1148,6 +1268,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1177,6 +1302,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1206,6 +1336,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1235,6 +1370,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1264,6 +1404,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1293,6 +1438,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1322,6 +1472,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1351,6 +1506,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1380,6 +1540,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1409,6 +1574,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1438,6 +1608,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1467,6 +1642,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1496,6 +1676,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1525,6 +1710,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1554,6 +1744,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1583,6 +1778,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1612,6 +1812,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1641,6 +1846,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1670,6 +1880,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1699,6 +1914,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1728,6 +1948,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1757,6 +1982,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1786,6 +2016,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1815,6 +2050,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1844,6 +2084,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1873,6 +2118,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1902,6 +2152,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1931,6 +2186,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1960,6 +2220,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1989,6 +2254,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2018,6 +2288,11 @@
           <t>BALÍK</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2043,6 +2318,11 @@
         <v>0.83</v>
       </c>
       <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2068,6 +2348,11 @@
         <v>1.02</v>
       </c>
       <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2093,6 +2378,11 @@
         <v>0.8</v>
       </c>
       <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2118,6 +2408,11 @@
         <v>0.8</v>
       </c>
       <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2143,6 +2438,11 @@
         <v>0.4</v>
       </c>
       <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2168,6 +2468,11 @@
         <v>0.15</v>
       </c>
       <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2193,6 +2498,11 @@
         <v>2</v>
       </c>
       <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2218,6 +2528,11 @@
         <v>2</v>
       </c>
       <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2243,6 +2558,11 @@
         <v>0.8</v>
       </c>
       <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2268,6 +2588,11 @@
         <v>0.9</v>
       </c>
       <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2293,6 +2618,11 @@
         <v>1.1</v>
       </c>
       <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2318,6 +2648,11 @@
         <v>1.6</v>
       </c>
       <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2343,6 +2678,11 @@
         <v>2.05</v>
       </c>
       <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2368,6 +2708,11 @@
         <v>1</v>
       </c>
       <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2393,6 +2738,11 @@
         <v>2.05</v>
       </c>
       <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2418,6 +2768,11 @@
         <v>1</v>
       </c>
       <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2443,6 +2798,11 @@
         <v>1</v>
       </c>
       <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2468,6 +2828,11 @@
         <v>2.05</v>
       </c>
       <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2493,6 +2858,11 @@
         <v>1</v>
       </c>
       <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2518,6 +2888,11 @@
         <v>2.05</v>
       </c>
       <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2543,6 +2918,11 @@
         <v>2.05</v>
       </c>
       <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2568,6 +2948,11 @@
         <v>1</v>
       </c>
       <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2593,6 +2978,11 @@
         <v>2.05</v>
       </c>
       <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2618,6 +3008,11 @@
         <v>1</v>
       </c>
       <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2643,6 +3038,11 @@
         <v>1</v>
       </c>
       <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2668,6 +3068,11 @@
         <v>2.05</v>
       </c>
       <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2693,6 +3098,11 @@
         <v>1</v>
       </c>
       <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2718,6 +3128,11 @@
         <v>1.3</v>
       </c>
       <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2743,6 +3158,11 @@
         <v>2.05</v>
       </c>
       <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2768,6 +3188,11 @@
         <v>1</v>
       </c>
       <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2793,6 +3218,11 @@
         <v>1</v>
       </c>
       <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2818,6 +3248,11 @@
         <v>2.05</v>
       </c>
       <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2843,6 +3278,11 @@
         <v>1</v>
       </c>
       <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2868,6 +3308,11 @@
         <v>1</v>
       </c>
       <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2893,6 +3338,11 @@
         <v>2.05</v>
       </c>
       <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2918,6 +3368,11 @@
         <v>1.01</v>
       </c>
       <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2943,6 +3398,11 @@
         <v>2</v>
       </c>
       <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2968,6 +3428,11 @@
         <v>0.95</v>
       </c>
       <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2993,6 +3458,11 @@
         <v>0.5</v>
       </c>
       <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3018,6 +3488,11 @@
         <v>1.32</v>
       </c>
       <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3043,6 +3518,11 @@
         <v>2.05</v>
       </c>
       <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3068,6 +3548,11 @@
         <v>1.48</v>
       </c>
       <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3093,6 +3578,11 @@
         <v>1.45</v>
       </c>
       <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3118,6 +3608,11 @@
         <v>2.05</v>
       </c>
       <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3143,6 +3638,11 @@
         <v>1.1</v>
       </c>
       <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3168,6 +3668,11 @@
         <v>1.05</v>
       </c>
       <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3193,6 +3698,11 @@
         <v>2.05</v>
       </c>
       <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3218,6 +3728,11 @@
         <v>1.28</v>
       </c>
       <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3243,6 +3758,11 @@
         <v>1.25</v>
       </c>
       <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3268,6 +3788,11 @@
         <v>2.05</v>
       </c>
       <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3293,6 +3818,11 @@
         <v>2.08</v>
       </c>
       <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3318,6 +3848,11 @@
         <v>1.05</v>
       </c>
       <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3343,6 +3878,11 @@
         <v>2.05</v>
       </c>
       <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3368,6 +3908,11 @@
         <v>1.05</v>
       </c>
       <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3393,6 +3938,11 @@
         <v>0.95</v>
       </c>
       <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3418,6 +3968,11 @@
         <v>2.05</v>
       </c>
       <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3443,6 +3998,11 @@
         <v>1.65</v>
       </c>
       <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3468,6 +4028,11 @@
         <v>0.85</v>
       </c>
       <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3493,6 +4058,11 @@
         <v>2.1</v>
       </c>
       <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3518,6 +4088,11 @@
         <v>2.05</v>
       </c>
       <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3543,6 +4118,11 @@
         <v>1.48</v>
       </c>
       <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3568,6 +4148,11 @@
         <v>1.45</v>
       </c>
       <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3593,6 +4178,11 @@
         <v>1</v>
       </c>
       <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3618,6 +4208,11 @@
         <v>2.05</v>
       </c>
       <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3643,6 +4238,11 @@
         <v>2</v>
       </c>
       <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3668,6 +4268,11 @@
         <v>0.83</v>
       </c>
       <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3693,6 +4298,11 @@
         <v>1.31</v>
       </c>
       <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3718,6 +4328,11 @@
         <v>0.84</v>
       </c>
       <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3743,6 +4358,11 @@
         <v>0.86</v>
       </c>
       <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3768,6 +4388,11 @@
         <v>1.12</v>
       </c>
       <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3793,6 +4418,11 @@
         <v>1.25</v>
       </c>
       <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3818,6 +4448,11 @@
         <v>0.82</v>
       </c>
       <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3843,6 +4478,11 @@
         <v>1.5</v>
       </c>
       <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3868,6 +4508,11 @@
         <v>2.05</v>
       </c>
       <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3893,6 +4538,11 @@
         <v>1.28</v>
       </c>
       <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3918,6 +4568,11 @@
         <v>1.25</v>
       </c>
       <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3943,6 +4598,11 @@
         <v>1.89</v>
       </c>
       <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3968,6 +4628,11 @@
         <v>0.66</v>
       </c>
       <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3993,6 +4658,11 @@
         <v>1.27</v>
       </c>
       <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4018,6 +4688,11 @@
         <v>2</v>
       </c>
       <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4043,6 +4718,11 @@
         <v>0.9</v>
       </c>
       <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4068,6 +4748,11 @@
         <v>0.9</v>
       </c>
       <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4093,6 +4778,11 @@
         <v>1.8</v>
       </c>
       <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4118,6 +4808,11 @@
         <v>1.97</v>
       </c>
       <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4143,6 +4838,11 @@
         <v>1.97</v>
       </c>
       <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4168,6 +4868,11 @@
         <v>0.2</v>
       </c>
       <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4193,6 +4898,11 @@
         <v>1.6</v>
       </c>
       <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4218,6 +4928,11 @@
         <v>1.4</v>
       </c>
       <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4243,6 +4958,11 @@
         <v>0.93</v>
       </c>
       <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4268,6 +4988,11 @@
         <v>1</v>
       </c>
       <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4293,6 +5018,11 @@
         <v>2.05</v>
       </c>
       <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4318,6 +5048,11 @@
         <v>0.9</v>
       </c>
       <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4343,6 +5078,11 @@
         <v>1</v>
       </c>
       <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4368,6 +5108,11 @@
         <v>2.05</v>
       </c>
       <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4393,6 +5138,11 @@
         <v>1</v>
       </c>
       <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4418,6 +5168,11 @@
         <v>2</v>
       </c>
       <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4443,6 +5198,11 @@
         <v>1.5</v>
       </c>
       <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4468,6 +5228,11 @@
         <v>0.88</v>
       </c>
       <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4493,6 +5258,11 @@
         <v>1.12</v>
       </c>
       <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4518,6 +5288,11 @@
         <v>0.6</v>
       </c>
       <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4543,6 +5318,11 @@
         <v>1.7</v>
       </c>
       <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4568,6 +5348,11 @@
         <v>1.8</v>
       </c>
       <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4593,6 +5378,11 @@
         <v>0.9</v>
       </c>
       <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4618,6 +5408,11 @@
         <v>1.05</v>
       </c>
       <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4643,6 +5438,11 @@
         <v>2.06</v>
       </c>
       <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4668,6 +5468,11 @@
         <v>1.5</v>
       </c>
       <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4693,6 +5498,11 @@
         <v>2.07</v>
       </c>
       <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4718,6 +5528,11 @@
         <v>1.45</v>
       </c>
       <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4743,6 +5558,11 @@
         <v>1.5</v>
       </c>
       <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4768,6 +5588,11 @@
         <v>2.07</v>
       </c>
       <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4793,6 +5618,11 @@
         <v>1.45</v>
       </c>
       <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4818,6 +5648,11 @@
         <v>1.5</v>
       </c>
       <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4843,6 +5678,11 @@
         <v>2.07</v>
       </c>
       <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4868,6 +5708,11 @@
         <v>1.45</v>
       </c>
       <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4893,6 +5738,11 @@
         <v>1.5</v>
       </c>
       <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4918,6 +5768,11 @@
         <v>2.07</v>
       </c>
       <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4943,6 +5798,11 @@
         <v>1.45</v>
       </c>
       <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4968,6 +5828,11 @@
         <v>1.85</v>
       </c>
       <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4993,6 +5858,11 @@
         <v>2.07</v>
       </c>
       <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5018,6 +5888,11 @@
         <v>0.95</v>
       </c>
       <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5043,6 +5918,11 @@
         <v>1.85</v>
       </c>
       <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5068,6 +5948,11 @@
         <v>2.07</v>
       </c>
       <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5093,6 +5978,11 @@
         <v>0.95</v>
       </c>
       <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5118,6 +6008,11 @@
         <v>2.05</v>
       </c>
       <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5143,6 +6038,11 @@
         <v>2.07</v>
       </c>
       <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5168,6 +6068,11 @@
         <v>1.05</v>
       </c>
       <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5193,6 +6098,11 @@
         <v>1.65</v>
       </c>
       <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5218,6 +6128,11 @@
         <v>2.07</v>
       </c>
       <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5243,6 +6158,11 @@
         <v>0.85</v>
       </c>
       <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5268,6 +6188,11 @@
         <v>1.65</v>
       </c>
       <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5293,6 +6218,11 @@
         <v>2.07</v>
       </c>
       <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5318,6 +6248,11 @@
         <v>0.85</v>
       </c>
       <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5343,6 +6278,11 @@
         <v>1.25</v>
       </c>
       <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5368,6 +6308,11 @@
         <v>2.07</v>
       </c>
       <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5393,6 +6338,11 @@
         <v>1.25</v>
       </c>
       <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5418,6 +6368,11 @@
         <v>1.25</v>
       </c>
       <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5443,6 +6398,11 @@
         <v>2.07</v>
       </c>
       <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5468,6 +6428,11 @@
         <v>1.25</v>
       </c>
       <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5493,6 +6458,11 @@
         <v>0.95</v>
       </c>
       <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5518,6 +6488,11 @@
         <v>2.07</v>
       </c>
       <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5543,6 +6518,11 @@
         <v>0.95</v>
       </c>
       <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5568,6 +6548,11 @@
         <v>0.95</v>
       </c>
       <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5593,6 +6578,11 @@
         <v>2.07</v>
       </c>
       <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5618,6 +6608,11 @@
         <v>0.95</v>
       </c>
       <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5643,6 +6638,11 @@
         <v>0.95</v>
       </c>
       <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5668,6 +6668,11 @@
         <v>2.07</v>
       </c>
       <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5693,6 +6698,11 @@
         <v>0.85</v>
       </c>
       <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5718,6 +6728,11 @@
         <v>1.05</v>
       </c>
       <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5743,6 +6758,11 @@
         <v>2.07</v>
       </c>
       <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5768,6 +6788,11 @@
         <v>1.05</v>
       </c>
       <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5793,6 +6818,11 @@
         <v>1.56</v>
       </c>
       <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5818,6 +6848,11 @@
         <v>2.09</v>
       </c>
       <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5843,6 +6878,11 @@
         <v>0.83</v>
       </c>
       <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5868,6 +6908,11 @@
         <v>0.95</v>
       </c>
       <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5893,6 +6938,11 @@
         <v>2.05</v>
       </c>
       <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5918,6 +6968,11 @@
         <v>1</v>
       </c>
       <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5943,6 +6998,11 @@
         <v>2</v>
       </c>
       <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5968,6 +7028,11 @@
         <v>1.35</v>
       </c>
       <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5993,6 +7058,11 @@
         <v>2.07</v>
       </c>
       <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6018,6 +7088,11 @@
         <v>0.85</v>
       </c>
       <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6043,6 +7118,11 @@
         <v>0.95</v>
       </c>
       <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6068,6 +7148,11 @@
         <v>2.05</v>
       </c>
       <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6093,6 +7178,11 @@
         <v>1</v>
       </c>
       <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6118,6 +7208,11 @@
         <v>1</v>
       </c>
       <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6143,6 +7238,11 @@
         <v>2.05</v>
       </c>
       <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6168,6 +7268,11 @@
         <v>1</v>
       </c>
       <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6193,6 +7298,11 @@
         <v>0.95</v>
       </c>
       <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6218,6 +7328,11 @@
         <v>2.05</v>
       </c>
       <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6243,6 +7358,11 @@
         <v>1</v>
       </c>
       <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6268,6 +7388,11 @@
         <v>1.1</v>
       </c>
       <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6293,6 +7418,11 @@
         <v>2.05</v>
       </c>
       <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6318,6 +7448,11 @@
         <v>1</v>
       </c>
       <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -6343,6 +7478,11 @@
         <v>2.05</v>
       </c>
       <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6368,6 +7508,11 @@
         <v>2.05</v>
       </c>
       <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -6393,6 +7538,11 @@
         <v>1</v>
       </c>
       <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6418,6 +7568,11 @@
         <v>2.05</v>
       </c>
       <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -6443,6 +7598,11 @@
         <v>1</v>
       </c>
       <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6468,6 +7628,11 @@
         <v>2</v>
       </c>
       <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -6493,6 +7658,11 @@
         <v>0.76</v>
       </c>
       <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6518,6 +7688,11 @@
         <v>0.5</v>
       </c>
       <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6543,6 +7718,11 @@
         <v>0.8</v>
       </c>
       <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6568,6 +7748,11 @@
         <v>1.7</v>
       </c>
       <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -6593,6 +7778,11 @@
         <v>1.85</v>
       </c>
       <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -6618,6 +7808,11 @@
         <v>2.05</v>
       </c>
       <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -6643,6 +7838,11 @@
         <v>0.9</v>
       </c>
       <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -6668,6 +7868,11 @@
         <v>1.7</v>
       </c>
       <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6693,6 +7898,11 @@
         <v>2.05</v>
       </c>
       <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6718,6 +7928,11 @@
         <v>0.96</v>
       </c>
       <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -6743,6 +7958,11 @@
         <v>2</v>
       </c>
       <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -6768,6 +7988,11 @@
         <v>1.2</v>
       </c>
       <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -6793,6 +8018,11 @@
         <v>0.93</v>
       </c>
       <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -6818,6 +8048,11 @@
         <v>0.82</v>
       </c>
       <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -6843,6 +8078,11 @@
         <v>1.02</v>
       </c>
       <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -6868,6 +8108,11 @@
         <v>0.89</v>
       </c>
       <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -6893,6 +8138,11 @@
         <v>0.77</v>
       </c>
       <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -6918,6 +8168,11 @@
         <v>0.89</v>
       </c>
       <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -6943,6 +8198,11 @@
         <v>0.43</v>
       </c>
       <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6968,6 +8228,11 @@
         <v>0.93</v>
       </c>
       <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6993,6 +8258,11 @@
         <v>0.93</v>
       </c>
       <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -7018,6 +8288,11 @@
         <v>1.07</v>
       </c>
       <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -7043,6 +8318,11 @@
         <v>1.07</v>
       </c>
       <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -7068,6 +8348,11 @@
         <v>1.04</v>
       </c>
       <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -7093,6 +8378,11 @@
         <v>0.82</v>
       </c>
       <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -7118,6 +8408,11 @@
         <v>1.14</v>
       </c>
       <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -7143,6 +8438,11 @@
         <v>1.02</v>
       </c>
       <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -7168,6 +8468,11 @@
         <v>0.82</v>
       </c>
       <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -7193,6 +8498,11 @@
         <v>1.83</v>
       </c>
       <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -7218,6 +8528,11 @@
         <v>0.42</v>
       </c>
       <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -7243,6 +8558,11 @@
         <v>0.61</v>
       </c>
       <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -7268,6 +8588,11 @@
         <v>1.22</v>
       </c>
       <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -7293,6 +8618,11 @@
         <v>1</v>
       </c>
       <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -7318,6 +8648,11 @@
         <v>1.06</v>
       </c>
       <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -7343,6 +8678,11 @@
         <v>0.91</v>
       </c>
       <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7368,6 +8708,11 @@
         <v>1.1</v>
       </c>
       <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -7393,6 +8738,11 @@
         <v>1.1</v>
       </c>
       <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -7418,6 +8768,11 @@
         <v>0.9</v>
       </c>
       <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -7443,6 +8798,11 @@
         <v>0.84</v>
       </c>
       <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -7468,6 +8828,11 @@
         <v>1.01</v>
       </c>
       <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -7493,6 +8858,11 @@
         <v>0.85</v>
       </c>
       <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -7518,6 +8888,11 @@
         <v>0.6</v>
       </c>
       <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -7543,6 +8918,11 @@
         <v>0.9</v>
       </c>
       <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -7568,6 +8948,11 @@
         <v>1.1</v>
       </c>
       <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -7593,6 +8978,11 @@
         <v>2.05</v>
       </c>
       <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -7618,6 +9008,11 @@
         <v>1.05</v>
       </c>
       <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -7643,6 +9038,11 @@
         <v>0.87</v>
       </c>
       <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -7668,6 +9068,11 @@
         <v>0.47</v>
       </c>
       <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -7693,6 +9098,11 @@
         <v>0.95</v>
       </c>
       <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -7718,6 +9128,11 @@
         <v>1.22</v>
       </c>
       <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -7743,6 +9158,11 @@
         <v>0.995</v>
       </c>
       <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -7768,6 +9188,11 @@
         <v>1.465</v>
       </c>
       <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -7793,6 +9218,11 @@
         <v>1.8</v>
       </c>
       <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -7818,6 +9248,11 @@
         <v>2.06</v>
       </c>
       <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -7843,6 +9278,11 @@
         <v>0.63</v>
       </c>
       <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -7868,6 +9308,11 @@
         <v>0.995</v>
       </c>
       <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -7893,6 +9338,11 @@
         <v>2.06</v>
       </c>
       <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -7918,6 +9368,11 @@
         <v>0.755</v>
       </c>
       <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -7943,6 +9398,11 @@
         <v>1.2</v>
       </c>
       <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -7968,6 +9428,11 @@
         <v>0.835</v>
       </c>
       <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -7993,6 +9458,11 @@
         <v>1.645</v>
       </c>
       <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -8018,6 +9488,11 @@
         <v>1.22</v>
       </c>
       <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -8043,6 +9518,11 @@
         <v>0.995</v>
       </c>
       <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -8068,6 +9548,11 @@
         <v>1.465</v>
       </c>
       <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -8093,6 +9578,11 @@
         <v>1.8</v>
       </c>
       <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -8118,6 +9608,11 @@
         <v>2.06</v>
       </c>
       <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -8143,6 +9638,11 @@
         <v>1.315</v>
       </c>
       <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -8168,6 +9668,11 @@
         <v>1.01</v>
       </c>
       <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -8193,6 +9698,11 @@
         <v>0.85</v>
       </c>
       <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -8218,6 +9728,11 @@
         <v>1.02</v>
       </c>
       <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -8243,6 +9758,11 @@
         <v>0.72</v>
       </c>
       <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -8268,6 +9788,11 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -8293,6 +9818,11 @@
         <v>0.42</v>
       </c>
       <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -8318,6 +9848,11 @@
         <v>0.42</v>
       </c>
       <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -8343,6 +9878,11 @@
         <v>1.02</v>
       </c>
       <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -8368,6 +9908,11 @@
         <v>0.89</v>
       </c>
       <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -8393,6 +9938,11 @@
         <v>2.06</v>
       </c>
       <c r="G310" t="inlineStr"/>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -8418,6 +9968,11 @@
         <v>1.06</v>
       </c>
       <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -8443,6 +9998,11 @@
         <v>1</v>
       </c>
       <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -8468,6 +10028,11 @@
         <v>0.23</v>
       </c>
       <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -8493,6 +10058,11 @@
         <v>0.73</v>
       </c>
       <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -8518,6 +10088,11 @@
         <v>0.83</v>
       </c>
       <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -8543,6 +10118,11 @@
         <v>0.78</v>
       </c>
       <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -8568,6 +10148,11 @@
         <v>0.79</v>
       </c>
       <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -8593,6 +10178,11 @@
         <v>0.78</v>
       </c>
       <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -8618,6 +10208,11 @@
         <v>0.87</v>
       </c>
       <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -8643,6 +10238,11 @@
         <v>0.78</v>
       </c>
       <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -8668,6 +10268,11 @@
         <v>0.77</v>
       </c>
       <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -8693,6 +10298,11 @@
         <v>1.7</v>
       </c>
       <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -8718,6 +10328,11 @@
         <v>2.05</v>
       </c>
       <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -8743,6 +10358,11 @@
         <v>0.8</v>
       </c>
       <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -8768,6 +10388,11 @@
         <v>0.5</v>
       </c>
       <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -8793,6 +10418,11 @@
         <v>1.43</v>
       </c>
       <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -8818,6 +10448,11 @@
         <v>0.8</v>
       </c>
       <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -8843,6 +10478,11 @@
         <v>1.2</v>
       </c>
       <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -8868,6 +10508,11 @@
         <v>1.05</v>
       </c>
       <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -8893,6 +10538,11 @@
         <v>0.85</v>
       </c>
       <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -8918,6 +10568,11 @@
         <v>0.05</v>
       </c>
       <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -8943,6 +10598,11 @@
         <v>0.05</v>
       </c>
       <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -8968,6 +10628,11 @@
         <v>0.22</v>
       </c>
       <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -8993,6 +10658,11 @@
         <v>1.705</v>
       </c>
       <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -9018,6 +10688,11 @@
         <v>1.105</v>
       </c>
       <c r="G335" t="inlineStr"/>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -9043,6 +10718,11 @@
         <v>0.05</v>
       </c>
       <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -9068,6 +10748,11 @@
         <v>0.08</v>
       </c>
       <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -9093,6 +10778,11 @@
         <v>0.26</v>
       </c>
       <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -9118,6 +10808,11 @@
         <v>1.025</v>
       </c>
       <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -9143,6 +10838,11 @@
         <v>0.88</v>
       </c>
       <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -9168,6 +10868,11 @@
         <v>0.75</v>
       </c>
       <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -9193,6 +10898,11 @@
         <v>1.02</v>
       </c>
       <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -9218,6 +10928,11 @@
         <v>1.05</v>
       </c>
       <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -9243,6 +10958,11 @@
         <v>0.74</v>
       </c>
       <c r="G344" t="inlineStr"/>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -9268,6 +10988,11 @@
         <v>0.42</v>
       </c>
       <c r="G345" t="inlineStr"/>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -9293,6 +11018,11 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="G346" t="inlineStr"/>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -9318,6 +11048,11 @@
         <v>1.02</v>
       </c>
       <c r="G347" t="inlineStr"/>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -9343,6 +11078,11 @@
         <v>1</v>
       </c>
       <c r="G348" t="inlineStr"/>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -9368,6 +11108,11 @@
         <v>0.42</v>
       </c>
       <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -9393,6 +11138,11 @@
         <v>0.42</v>
       </c>
       <c r="G350" t="inlineStr"/>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -9418,6 +11168,11 @@
         <v>0.99</v>
       </c>
       <c r="G351" t="inlineStr"/>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -9443,6 +11198,11 @@
         <v>0.73</v>
       </c>
       <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -9468,6 +11228,11 @@
         <v>0.2</v>
       </c>
       <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -9493,6 +11258,11 @@
         <v>0.1</v>
       </c>
       <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -9518,6 +11288,11 @@
         <v>0.2</v>
       </c>
       <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -9543,6 +11318,11 @@
         <v>0.84</v>
       </c>
       <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -9568,6 +11348,11 @@
         <v>0.845</v>
       </c>
       <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -9593,6 +11378,11 @@
         <v>1.32</v>
       </c>
       <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -9618,6 +11408,11 @@
         <v>1.62</v>
       </c>
       <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -9643,6 +11438,11 @@
         <v>1.86</v>
       </c>
       <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -9668,6 +11468,11 @@
         <v>2</v>
       </c>
       <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -9693,6 +11498,11 @@
         <v>1.13</v>
       </c>
       <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -9718,6 +11528,11 @@
         <v>0.9</v>
       </c>
       <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -9743,6 +11558,11 @@
         <v>0.9</v>
       </c>
       <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -9768,6 +11588,11 @@
         <v>1.8</v>
       </c>
       <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -9793,6 +11618,11 @@
         <v>0.9</v>
       </c>
       <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -9818,6 +11648,11 @@
         <v>1</v>
       </c>
       <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -9843,6 +11678,11 @@
         <v>2.05</v>
       </c>
       <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -9868,6 +11708,11 @@
         <v>1</v>
       </c>
       <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -9893,6 +11738,11 @@
         <v>1</v>
       </c>
       <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -9918,6 +11768,11 @@
         <v>2.05</v>
       </c>
       <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -9943,6 +11798,11 @@
         <v>1</v>
       </c>
       <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -9968,6 +11828,11 @@
         <v>2.05</v>
       </c>
       <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -9993,6 +11858,11 @@
         <v>1</v>
       </c>
       <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -10018,6 +11888,11 @@
         <v>1</v>
       </c>
       <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -10043,6 +11918,11 @@
         <v>2.05</v>
       </c>
       <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -10068,6 +11948,11 @@
         <v>1</v>
       </c>
       <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -10093,6 +11978,11 @@
         <v>1.1</v>
       </c>
       <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -10118,6 +12008,11 @@
         <v>2.05</v>
       </c>
       <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -10143,6 +12038,11 @@
         <v>1.05</v>
       </c>
       <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -10168,6 +12068,11 @@
         <v>1</v>
       </c>
       <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -10193,6 +12098,11 @@
         <v>2.05</v>
       </c>
       <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -10218,6 +12128,11 @@
         <v>0.9</v>
       </c>
       <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -10243,6 +12158,11 @@
         <v>1</v>
       </c>
       <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -10268,6 +12188,11 @@
         <v>2.05</v>
       </c>
       <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -10293,6 +12218,11 @@
         <v>0.9</v>
       </c>
       <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -10318,6 +12248,11 @@
         <v>1.7</v>
       </c>
       <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -10343,6 +12278,11 @@
         <v>2.05</v>
       </c>
       <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -10368,6 +12308,11 @@
         <v>0.8</v>
       </c>
       <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -10393,6 +12338,11 @@
         <v>0.1</v>
       </c>
       <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -10418,6 +12368,11 @@
         <v>0.1</v>
       </c>
       <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -10443,6 +12398,11 @@
         <v>0.2</v>
       </c>
       <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -10468,6 +12428,11 @@
         <v>1.9</v>
       </c>
       <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -10493,6 +12458,11 @@
         <v>0.05</v>
       </c>
       <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -10518,6 +12488,11 @@
         <v>0.05</v>
       </c>
       <c r="G395" t="inlineStr"/>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -10543,6 +12518,11 @@
         <v>0.11</v>
       </c>
       <c r="G396" t="inlineStr"/>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -10568,6 +12548,11 @@
         <v>1.04</v>
       </c>
       <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -10593,6 +12578,11 @@
         <v>0.85</v>
       </c>
       <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -10618,6 +12608,11 @@
         <v>1.865</v>
       </c>
       <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -10643,6 +12638,11 @@
         <v>1.865</v>
       </c>
       <c r="G400" t="inlineStr"/>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -10668,6 +12668,11 @@
         <v>1.865</v>
       </c>
       <c r="G401" t="inlineStr"/>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -10693,6 +12698,11 @@
         <v>1.005</v>
       </c>
       <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -10718,6 +12728,11 @@
         <v>0.74</v>
       </c>
       <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -10743,6 +12758,11 @@
         <v>0.05</v>
       </c>
       <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -10768,6 +12788,11 @@
         <v>0.05</v>
       </c>
       <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -10793,6 +12818,11 @@
         <v>0.13</v>
       </c>
       <c r="G406" t="inlineStr"/>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -10818,6 +12848,11 @@
         <v>0.05</v>
       </c>
       <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -10843,6 +12878,11 @@
         <v>0.05</v>
       </c>
       <c r="G408" t="inlineStr"/>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -10868,6 +12908,11 @@
         <v>0.13</v>
       </c>
       <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -10893,6 +12938,11 @@
         <v>0.05</v>
       </c>
       <c r="G410" t="inlineStr"/>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -10918,6 +12968,11 @@
         <v>0.05</v>
       </c>
       <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -10943,6 +12998,11 @@
         <v>0.13</v>
       </c>
       <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -10968,6 +13028,11 @@
         <v>0.1</v>
       </c>
       <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -10993,6 +13058,11 @@
         <v>0.1</v>
       </c>
       <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -11018,6 +13088,11 @@
         <v>0.055</v>
       </c>
       <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -11043,6 +13118,11 @@
         <v>0.05</v>
       </c>
       <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -11068,6 +13148,11 @@
         <v>0.11</v>
       </c>
       <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -11093,6 +13178,11 @@
         <v>0.055</v>
       </c>
       <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -11118,6 +13208,11 @@
         <v>0.05</v>
       </c>
       <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -11143,6 +13238,11 @@
         <v>0.11</v>
       </c>
       <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -11168,6 +13268,11 @@
         <v>0.12</v>
       </c>
       <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -11193,6 +13298,11 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G422" t="inlineStr"/>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -11218,6 +13328,11 @@
         <v>0.12</v>
       </c>
       <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -11243,6 +13358,11 @@
         <v>1.6</v>
       </c>
       <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -11268,6 +13388,11 @@
         <v>0.06</v>
       </c>
       <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -11293,6 +13418,11 @@
         <v>0.05</v>
       </c>
       <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -11318,6 +13448,11 @@
         <v>0.12</v>
       </c>
       <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -11343,6 +13478,11 @@
         <v>0.2</v>
       </c>
       <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -11368,6 +13508,11 @@
         <v>0.14</v>
       </c>
       <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -11393,6 +13538,11 @@
         <v>0.08</v>
       </c>
       <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -11418,6 +13568,11 @@
         <v>0.06</v>
       </c>
       <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -11443,6 +13598,11 @@
         <v>0.05</v>
       </c>
       <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -11468,6 +13628,11 @@
         <v>0.12</v>
       </c>
       <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -11493,6 +13658,11 @@
         <v>0.83</v>
       </c>
       <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -11518,6 +13688,11 @@
         <v>0.83</v>
       </c>
       <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -11543,6 +13718,11 @@
         <v>0.05</v>
       </c>
       <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -11568,6 +13748,11 @@
         <v>0.11</v>
       </c>
       <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -11593,6 +13778,11 @@
         <v>0.11</v>
       </c>
       <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -11618,6 +13808,11 @@
         <v>0.83</v>
       </c>
       <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -11643,6 +13838,11 @@
         <v>0.83</v>
       </c>
       <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -11668,6 +13868,11 @@
         <v>0.1</v>
       </c>
       <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -11693,6 +13898,11 @@
         <v>0.08</v>
       </c>
       <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -11718,6 +13928,11 @@
         <v>0.12</v>
       </c>
       <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -11743,6 +13958,11 @@
         <v>0.55</v>
       </c>
       <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -11768,6 +13988,11 @@
         <v>0.5</v>
       </c>
       <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -11793,6 +14018,11 @@
         <v>0.06</v>
       </c>
       <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -11818,6 +14048,11 @@
         <v>0.08</v>
       </c>
       <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -11843,6 +14078,11 @@
         <v>0.13</v>
       </c>
       <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -11868,6 +14108,11 @@
         <v>2</v>
       </c>
       <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -11893,6 +14138,11 @@
         <v>0.06</v>
       </c>
       <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -11918,6 +14168,11 @@
         <v>0.08</v>
       </c>
       <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -11943,6 +14198,11 @@
         <v>0.13</v>
       </c>
       <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -11968,6 +14228,11 @@
         <v>2.05</v>
       </c>
       <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -11993,6 +14258,11 @@
         <v>0.13</v>
       </c>
       <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -12018,6 +14288,11 @@
         <v>0.1</v>
       </c>
       <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -12043,6 +14318,11 @@
         <v>1.1</v>
       </c>
       <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -12068,6 +14348,11 @@
         <v>2.05</v>
       </c>
       <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -12093,6 +14378,11 @@
         <v>1.1</v>
       </c>
       <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -12118,6 +14408,11 @@
         <v>1.05</v>
       </c>
       <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -12143,6 +14438,11 @@
         <v>1.7</v>
       </c>
       <c r="G460" t="inlineStr"/>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -12168,6 +14468,11 @@
         <v>1.4</v>
       </c>
       <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -12193,6 +14498,11 @@
         <v>1.1</v>
       </c>
       <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -12218,6 +14528,11 @@
         <v>2.05</v>
       </c>
       <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -12243,6 +14558,11 @@
         <v>1</v>
       </c>
       <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -12268,6 +14588,11 @@
         <v>2</v>
       </c>
       <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -12293,6 +14618,11 @@
         <v>2</v>
       </c>
       <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -12318,6 +14648,11 @@
         <v>1</v>
       </c>
       <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -12343,6 +14678,11 @@
         <v>2.05</v>
       </c>
       <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -12368,6 +14708,11 @@
         <v>1</v>
       </c>
       <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -12393,6 +14738,11 @@
         <v>2.07</v>
       </c>
       <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -12418,6 +14768,11 @@
         <v>1.1</v>
       </c>
       <c r="G471" t="inlineStr"/>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -12443,6 +14798,11 @@
         <v>0.97</v>
       </c>
       <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -12468,6 +14828,11 @@
         <v>2</v>
       </c>
       <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -12493,6 +14858,11 @@
         <v>1.15</v>
       </c>
       <c r="G474" t="inlineStr"/>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -12518,6 +14888,11 @@
         <v>1</v>
       </c>
       <c r="G475" t="inlineStr"/>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -12543,6 +14918,11 @@
         <v>1.35</v>
       </c>
       <c r="G476" t="inlineStr"/>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -12568,6 +14948,11 @@
         <v>1.9</v>
       </c>
       <c r="G477" t="inlineStr"/>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -12593,6 +14978,11 @@
         <v>2.07</v>
       </c>
       <c r="G478" t="inlineStr"/>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -12618,6 +15008,11 @@
         <v>0.9</v>
       </c>
       <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -12643,6 +15038,11 @@
         <v>1.1</v>
       </c>
       <c r="G480" t="inlineStr"/>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -12668,6 +15068,11 @@
         <v>2</v>
       </c>
       <c r="G481" t="inlineStr"/>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -12693,6 +15098,11 @@
         <v>0.9</v>
       </c>
       <c r="G482" t="inlineStr"/>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -12718,6 +15128,11 @@
         <v>2.05</v>
       </c>
       <c r="G483" t="inlineStr"/>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -12743,6 +15158,11 @@
         <v>1.1</v>
       </c>
       <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -12768,6 +15188,11 @@
         <v>1.05</v>
       </c>
       <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -12793,6 +15218,11 @@
         <v>0.9</v>
       </c>
       <c r="G486" t="inlineStr"/>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -12818,6 +15248,11 @@
         <v>2.07</v>
       </c>
       <c r="G487" t="inlineStr"/>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -12843,6 +15278,11 @@
         <v>0.8</v>
       </c>
       <c r="G488" t="inlineStr"/>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -12868,6 +15308,11 @@
         <v>2.05</v>
       </c>
       <c r="G489" t="inlineStr"/>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -12893,6 +15338,11 @@
         <v>1.85</v>
       </c>
       <c r="G490" t="inlineStr"/>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -12918,6 +15368,11 @@
         <v>0.9</v>
       </c>
       <c r="G491" t="inlineStr"/>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -12943,6 +15398,11 @@
         <v>0.82</v>
       </c>
       <c r="G492" t="inlineStr"/>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -12968,6 +15428,11 @@
         <v>1.86</v>
       </c>
       <c r="G493" t="inlineStr"/>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -12993,6 +15458,11 @@
         <v>0.65</v>
       </c>
       <c r="G494" t="inlineStr"/>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -13018,6 +15488,11 @@
         <v>1.229</v>
       </c>
       <c r="G495" t="inlineStr"/>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -13043,6 +15518,11 @@
         <v>1.25</v>
       </c>
       <c r="G496" t="inlineStr"/>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -13068,6 +15548,11 @@
         <v>1.64</v>
       </c>
       <c r="G497" t="inlineStr"/>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -13093,6 +15578,11 @@
         <v>0.05</v>
       </c>
       <c r="G498" t="inlineStr"/>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -13118,6 +15608,11 @@
         <v>0.05</v>
       </c>
       <c r="G499" t="inlineStr"/>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -13143,6 +15638,11 @@
         <v>0.13</v>
       </c>
       <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -13168,6 +15668,11 @@
         <v>0.05</v>
       </c>
       <c r="G501" t="inlineStr"/>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -13193,6 +15698,11 @@
         <v>0.05</v>
       </c>
       <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -13218,6 +15728,11 @@
         <v>0.13</v>
       </c>
       <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -13243,6 +15758,11 @@
         <v>0.05</v>
       </c>
       <c r="G504" t="inlineStr"/>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -13268,6 +15788,11 @@
         <v>0.05</v>
       </c>
       <c r="G505" t="inlineStr"/>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -13293,6 +15818,11 @@
         <v>0.13</v>
       </c>
       <c r="G506" t="inlineStr"/>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -13318,6 +15848,11 @@
         <v>0.05</v>
       </c>
       <c r="G507" t="inlineStr"/>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -13343,6 +15878,11 @@
         <v>0.05</v>
       </c>
       <c r="G508" t="inlineStr"/>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -13368,6 +15908,11 @@
         <v>0.13</v>
       </c>
       <c r="G509" t="inlineStr"/>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -13393,6 +15938,11 @@
         <v>0.05</v>
       </c>
       <c r="G510" t="inlineStr"/>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -13418,6 +15968,11 @@
         <v>0.05</v>
       </c>
       <c r="G511" t="inlineStr"/>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -13443,6 +15998,11 @@
         <v>0.13</v>
       </c>
       <c r="G512" t="inlineStr"/>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -13468,6 +16028,11 @@
         <v>0.99</v>
       </c>
       <c r="G513" t="inlineStr"/>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -13493,6 +16058,11 @@
         <v>0.73</v>
       </c>
       <c r="G514" t="inlineStr"/>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -13518,6 +16088,11 @@
         <v>1</v>
       </c>
       <c r="G515" t="inlineStr"/>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -13543,6 +16118,11 @@
         <v>1.04</v>
       </c>
       <c r="G516" t="inlineStr"/>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -13568,6 +16148,11 @@
         <v>0.85</v>
       </c>
       <c r="G517" t="inlineStr"/>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -13593,6 +16178,11 @@
         <v>0.05</v>
       </c>
       <c r="G518" t="inlineStr"/>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -13618,6 +16208,11 @@
         <v>0.05</v>
       </c>
       <c r="G519" t="inlineStr"/>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -13643,6 +16238,11 @@
         <v>0.26</v>
       </c>
       <c r="G520" t="inlineStr"/>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -13668,6 +16268,11 @@
         <v>0.7</v>
       </c>
       <c r="G521" t="inlineStr"/>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -13693,6 +16298,11 @@
         <v>2</v>
       </c>
       <c r="G522" t="inlineStr"/>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -13718,6 +16328,11 @@
         <v>1.88</v>
       </c>
       <c r="G523" t="inlineStr"/>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -13743,6 +16358,11 @@
         <v>0.79</v>
       </c>
       <c r="G524" t="inlineStr"/>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -13768,6 +16388,11 @@
         <v>1.86</v>
       </c>
       <c r="G525" t="inlineStr"/>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -13793,6 +16418,11 @@
         <v>0.79</v>
       </c>
       <c r="G526" t="inlineStr"/>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -13818,6 +16448,11 @@
         <v>1.86</v>
       </c>
       <c r="G527" t="inlineStr"/>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -13843,6 +16478,11 @@
         <v>0.25</v>
       </c>
       <c r="G528" t="inlineStr"/>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -13868,6 +16508,11 @@
         <v>0.91</v>
       </c>
       <c r="G529" t="inlineStr"/>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -13893,6 +16538,11 @@
         <v>1.35</v>
       </c>
       <c r="G530" t="inlineStr"/>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -13918,6 +16568,11 @@
         <v>1.35</v>
       </c>
       <c r="G531" t="inlineStr"/>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -13943,6 +16598,11 @@
         <v>0.8</v>
       </c>
       <c r="G532" t="inlineStr"/>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -13968,6 +16628,11 @@
         <v>2.05</v>
       </c>
       <c r="G533" t="inlineStr"/>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -13993,6 +16658,11 @@
         <v>1</v>
       </c>
       <c r="G534" t="inlineStr"/>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -14018,6 +16688,11 @@
         <v>2.05</v>
       </c>
       <c r="G535" t="inlineStr"/>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -14043,6 +16718,11 @@
         <v>1</v>
       </c>
       <c r="G536" t="inlineStr"/>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -14068,6 +16748,11 @@
         <v>0.9</v>
       </c>
       <c r="G537" t="inlineStr"/>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -14093,6 +16778,11 @@
         <v>1.2</v>
       </c>
       <c r="G538" t="inlineStr"/>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -14118,6 +16808,11 @@
         <v>2.05</v>
       </c>
       <c r="G539" t="inlineStr"/>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -14143,6 +16838,11 @@
         <v>2.05</v>
       </c>
       <c r="G540" t="inlineStr"/>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -14168,6 +16868,11 @@
         <v>2.05</v>
       </c>
       <c r="G541" t="inlineStr"/>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -14193,6 +16898,11 @@
         <v>2.07</v>
       </c>
       <c r="G542" t="inlineStr"/>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -14218,6 +16928,11 @@
         <v>0.8</v>
       </c>
       <c r="G543" t="inlineStr"/>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -14243,6 +16958,11 @@
         <v>0.8</v>
       </c>
       <c r="G544" t="inlineStr"/>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -14268,6 +16988,11 @@
         <v>2.07</v>
       </c>
       <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -14293,6 +17018,11 @@
         <v>0.8</v>
       </c>
       <c r="G546" t="inlineStr"/>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -14318,6 +17048,11 @@
         <v>0.8</v>
       </c>
       <c r="G547" t="inlineStr"/>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -14343,6 +17078,11 @@
         <v>2.07</v>
       </c>
       <c r="G548" t="inlineStr"/>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -14368,6 +17108,11 @@
         <v>1.4</v>
       </c>
       <c r="G549" t="inlineStr"/>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -14393,6 +17138,11 @@
         <v>1.4</v>
       </c>
       <c r="G550" t="inlineStr"/>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -14418,6 +17168,11 @@
         <v>2.07</v>
       </c>
       <c r="G551" t="inlineStr"/>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -14443,6 +17198,11 @@
         <v>1.4</v>
       </c>
       <c r="G552" t="inlineStr"/>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -14468,6 +17228,11 @@
         <v>1.4</v>
       </c>
       <c r="G553" t="inlineStr"/>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -14493,6 +17258,11 @@
         <v>2.05</v>
       </c>
       <c r="G554" t="inlineStr"/>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -14518,6 +17288,11 @@
         <v>1</v>
       </c>
       <c r="G555" t="inlineStr"/>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -14543,6 +17318,11 @@
         <v>0.9</v>
       </c>
       <c r="G556" t="inlineStr"/>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -14568,6 +17348,11 @@
         <v>0.8</v>
       </c>
       <c r="G557" t="inlineStr"/>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -14593,6 +17378,11 @@
         <v>1.43</v>
       </c>
       <c r="G558" t="inlineStr"/>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -14618,6 +17408,11 @@
         <v>0.9</v>
       </c>
       <c r="G559" t="inlineStr"/>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -14643,6 +17438,11 @@
         <v>0.9</v>
       </c>
       <c r="G560" t="inlineStr"/>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -14668,6 +17468,11 @@
         <v>2.07</v>
       </c>
       <c r="G561" t="inlineStr"/>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -14693,6 +17498,11 @@
         <v>2</v>
       </c>
       <c r="G562" t="inlineStr"/>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -14718,6 +17528,11 @@
         <v>1</v>
       </c>
       <c r="G563" t="inlineStr"/>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -14743,6 +17558,11 @@
         <v>1</v>
       </c>
       <c r="G564" t="inlineStr"/>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -14768,6 +17588,11 @@
         <v>2.05</v>
       </c>
       <c r="G565" t="inlineStr"/>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -14793,6 +17618,11 @@
         <v>1</v>
       </c>
       <c r="G566" t="inlineStr"/>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -14818,6 +17648,11 @@
         <v>2.05</v>
       </c>
       <c r="G567" t="inlineStr"/>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -14843,6 +17678,11 @@
         <v>0.9</v>
       </c>
       <c r="G568" t="inlineStr"/>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -14868,6 +17708,11 @@
         <v>1.42</v>
       </c>
       <c r="G569" t="inlineStr"/>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -14893,6 +17738,11 @@
         <v>0.78</v>
       </c>
       <c r="G570" t="inlineStr"/>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -14918,6 +17768,11 @@
         <v>0.78</v>
       </c>
       <c r="G571" t="inlineStr"/>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -14943,6 +17798,11 @@
         <v>0.91</v>
       </c>
       <c r="G572" t="inlineStr"/>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -14968,6 +17828,11 @@
         <v>0.05</v>
       </c>
       <c r="G573" t="inlineStr"/>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -14993,6 +17858,11 @@
         <v>2</v>
       </c>
       <c r="G574" t="inlineStr"/>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -15018,6 +17888,11 @@
         <v>0.54</v>
       </c>
       <c r="G575" t="inlineStr"/>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -15043,6 +17918,11 @@
         <v>2</v>
       </c>
       <c r="G576" t="inlineStr"/>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -15068,6 +17948,11 @@
         <v>2</v>
       </c>
       <c r="G577" t="inlineStr"/>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -15093,6 +17978,11 @@
         <v>1</v>
       </c>
       <c r="G578" t="inlineStr"/>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -15118,6 +18008,11 @@
         <v>2.05</v>
       </c>
       <c r="G579" t="inlineStr"/>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -15143,6 +18038,11 @@
         <v>1.3</v>
       </c>
       <c r="G580" t="inlineStr"/>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -15168,6 +18068,11 @@
         <v>2.05</v>
       </c>
       <c r="G581" t="inlineStr"/>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -15193,6 +18098,11 @@
         <v>1</v>
       </c>
       <c r="G582" t="inlineStr"/>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -15218,6 +18128,11 @@
         <v>2.05</v>
       </c>
       <c r="G583" t="inlineStr"/>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -15243,6 +18158,11 @@
         <v>1</v>
       </c>
       <c r="G584" t="inlineStr"/>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -15268,6 +18188,11 @@
         <v>1.02</v>
       </c>
       <c r="G585" t="inlineStr"/>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -15293,6 +18218,11 @@
         <v>0.73</v>
       </c>
       <c r="G586" t="inlineStr"/>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -15318,6 +18248,11 @@
         <v>0.85</v>
       </c>
       <c r="G587" t="inlineStr"/>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -15343,6 +18278,11 @@
         <v>1.68</v>
       </c>
       <c r="G588" t="inlineStr"/>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -15368,6 +18308,11 @@
         <v>1.07</v>
       </c>
       <c r="G589" t="inlineStr"/>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -15393,6 +18338,11 @@
         <v>1.9</v>
       </c>
       <c r="G590" t="inlineStr"/>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -15418,6 +18368,11 @@
         <v>2.07</v>
       </c>
       <c r="G591" t="inlineStr"/>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -15443,6 +18398,71 @@
         <v>1.4</v>
       </c>
       <c r="G592" t="inlineStr"/>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>TOPTRANS</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Patrová postel ELPY MID SOLID vč. roštu</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>8X8-5A 1/2</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>25</v>
+      </c>
+      <c r="D593" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E593" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F593" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G593" t="inlineStr"/>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Patrová postel ELPY MID SOLID vč. roštu</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>8X8-5A 2/2</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>30</v>
+      </c>
+      <c r="D594" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E594" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F594" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G594" t="inlineStr"/>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H594"/>
+  <dimension ref="A1:H597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18464,6 +18464,96 @@
         </is>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MAREK PINE z masivu borovice 90x200 cm včetně roštů a zábrany  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>LPW-03 1/3</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>27</v>
+      </c>
+      <c r="D595" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E595" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F595" t="n">
+        <v>1</v>
+      </c>
+      <c r="G595" t="inlineStr"/>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MAREK PINE z masivu borovice 90x200 cm včetně roštů a zábrany  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>LPW-03 2/3</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>19</v>
+      </c>
+      <c r="D596" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E596" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F596" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G596" t="inlineStr"/>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MAREK PINE z masivu borovice 90x200 cm včetně roštů a zábrany  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>LPW-03 3/3</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>24</v>
+      </c>
+      <c r="D597" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E597" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F597" t="n">
+        <v>1</v>
+      </c>
+      <c r="G597" t="inlineStr"/>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H597"/>
+  <dimension ref="A1:H599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18554,6 +18554,66 @@
         </is>
       </c>
     </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Dětská postel z masivu se zábranou ŽOFKA PINE – včetně roštu | Borovice | Nosnost 120 kg  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>LPO-26 1/2</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>20</v>
+      </c>
+      <c r="D598" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E598" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F598" t="n">
+        <v>1</v>
+      </c>
+      <c r="G598" t="inlineStr"/>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Dětská postel z masivu se zábranou ŽOFKA PINE – včetně roštu | Borovice | Nosnost 120 kg  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>LPO-26 2/2</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>28</v>
+      </c>
+      <c r="D599" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E599" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F599" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G599" t="inlineStr"/>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H599"/>
+  <dimension ref="A1:H601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18614,6 +18614,66 @@
         </is>
       </c>
     </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Patrová postel ELPY MAX PLUS SOLID 120/140x200 vč. roštu</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>8X8-4B 1/2</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>25</v>
+      </c>
+      <c r="D600" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E600" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F600" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G600" t="inlineStr"/>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Patrová postel ELPY MAX PLUS SOLID 120/140x200 vč. roštu</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>8X8-4B 2/2</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>30</v>
+      </c>
+      <c r="D601" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E601" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F601" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G601" t="inlineStr"/>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H601"/>
+  <dimension ref="A1:H602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18674,6 +18674,36 @@
         </is>
       </c>
     </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Dětská postel se zábranou TUTTI II SOLID 8x8 vč. roštu</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>8X8-1C</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>30</v>
+      </c>
+      <c r="D602" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E602" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F602" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G602" t="inlineStr"/>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H602"/>
+  <dimension ref="A1:H605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18704,6 +18704,96 @@
         </is>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Patrová postel ADRIANA PINE vč. roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>LP-04 1/3</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>19</v>
+      </c>
+      <c r="D603" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E603" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F603" t="n">
+        <v>1</v>
+      </c>
+      <c r="G603" t="inlineStr"/>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Patrová postel ADRIANA PINE vč. roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>LP-04 2/3</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>27</v>
+      </c>
+      <c r="D604" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E604" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F604" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G604" t="inlineStr"/>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Patrová postel ADRIANA PINE vč. roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>LP-04 3/3</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>24</v>
+      </c>
+      <c r="D605" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E605" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F605" t="n">
+        <v>1</v>
+      </c>
+      <c r="G605" t="inlineStr"/>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H605"/>
+  <dimension ref="A1:H607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18794,6 +18794,66 @@
         </is>
       </c>
     </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Dětská postel ZARA KIDBED ONE ze dřeva + rošt  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>LPO-10 1/2</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>20</v>
+      </c>
+      <c r="D606" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E606" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F606" t="n">
+        <v>1</v>
+      </c>
+      <c r="G606" t="inlineStr"/>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Dětská postel ZARA KIDBED ONE ze dřeva + rošt  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>LPO-10 2/2</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>28</v>
+      </c>
+      <c r="D607" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E607" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F607" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G607" t="inlineStr"/>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H607"/>
+  <dimension ref="A1:H608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18854,6 +18854,36 @@
         </is>
       </c>
     </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Rohový psací stůl RYDEN se zásuvkami a nástavcem 123 × 120 cm</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>50</v>
+      </c>
+      <c r="D608" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E608" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F608" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G608" t="inlineStr"/>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H608"/>
+  <dimension ref="A1:H609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18884,6 +18884,36 @@
         </is>
       </c>
     </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Přebalovací komoda PAULA 2v1 s přebalovacím pultem pro miminko a dětská komoda</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>KOMODA-PREBAL-K-3+3</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>38</v>
+      </c>
+      <c r="D609" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E609" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F609" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G609" t="inlineStr"/>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H609"/>
+  <dimension ref="A1:H610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18914,6 +18914,36 @@
         </is>
       </c>
     </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Zdravotní matrace SANJA 18 cm – ortopedická sendvičová matrace s VISCO pěnou a 7 anatomickými zónami</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>KOMODA-PREBAL-K-3+3</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>20</v>
+      </c>
+      <c r="D610" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E610" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F610" t="n">
+        <v>2</v>
+      </c>
+      <c r="G610" t="inlineStr"/>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -18922,7 +18922,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>KOMODA-PREBAL-K-3+3</t>
+          <t>VISCO-WAVE</t>
         </is>
       </c>
       <c r="C610" t="n">

--- a/products.xlsx
+++ b/products.xlsx
@@ -1950,7 +1950,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -16480,7 +16480,7 @@
       <c r="G528" t="inlineStr"/>
       <c r="H528" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -18040,7 +18040,7 @@
       <c r="G580" t="inlineStr"/>
       <c r="H580" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -18070,7 +18070,7 @@
       <c r="G581" t="inlineStr"/>
       <c r="H581" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -2710,7 +2710,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -14650,7 +14650,7 @@
       <c r="G467" t="inlineStr"/>
       <c r="H467" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14680,7 @@
       <c r="G468" t="inlineStr"/>
       <c r="H468" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -14710,7 +14710,7 @@
       <c r="G469" t="inlineStr"/>
       <c r="H469" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -16780,7 +16780,7 @@
       <c r="G538" t="inlineStr"/>
       <c r="H538" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -16810,7 +16810,7 @@
       <c r="G539" t="inlineStr"/>
       <c r="H539" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -7180,7 +7180,7 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -11650,7 +11650,7 @@
       <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -11680,7 +11680,7 @@
       <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
       <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -14470,7 +14470,7 @@
       <c r="G461" t="inlineStr"/>
       <c r="H461" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -3040,7 +3040,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -5050,7 +5050,7 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -2950,7 +2950,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -16840,7 +16840,7 @@
       <c r="G540" t="inlineStr"/>
       <c r="H540" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -16870,7 +16870,7 @@
       <c r="G541" t="inlineStr"/>
       <c r="H541" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H610"/>
+  <dimension ref="A1:H612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18944,6 +18944,66 @@
         </is>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 160x200 cm BOSTON z masivní borovice včetně roštu</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>BOSTON-160 1/2</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>40</v>
+      </c>
+      <c r="D611" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E611" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F611" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G611" t="inlineStr"/>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 160x200 cm BOSTON z masivní borovice včetně roštu</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>BOSTON-160 2/2</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>12</v>
+      </c>
+      <c r="D612" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E612" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F612" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G612" t="inlineStr"/>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H612"/>
+  <dimension ref="A1:H614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19004,6 +19004,66 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Postel BESKYD 90x200 cm z masivní borovice s roštem | Jednolůžková dřevěná postel</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>BESKYD-90 1/2</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>18</v>
+      </c>
+      <c r="D613" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E613" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F613" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G613" t="inlineStr"/>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Postel BESKYD 90x200 cm z masivní borovice s roštem | Jednolůžková dřevěná postel</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>BESKYD-90 2/2</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>12</v>
+      </c>
+      <c r="D614" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E614" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F614" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G614" t="inlineStr"/>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H614"/>
+  <dimension ref="A1:H616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19064,6 +19064,66 @@
         </is>
       </c>
     </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120x200 cm z masivu borovice VMK3B surová</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>VMK-3B-120 1/2</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>22</v>
+      </c>
+      <c r="D615" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E615" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F615" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G615" t="inlineStr"/>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120x200 cm z masivu borovice VMK3B surová</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>VMK-3B-120 2/2</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>15</v>
+      </c>
+      <c r="D616" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E616" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F616" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G616" t="inlineStr"/>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H616"/>
+  <dimension ref="A1:H618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19124,6 +19124,66 @@
         </is>
       </c>
     </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 160x200 masiv borovice - VMK14B</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>VMK-14B-160 1/2</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>25</v>
+      </c>
+      <c r="D617" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E617" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F617" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G617" t="inlineStr"/>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 160x200 masiv borovice - VMK14B</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>VMK-14B-160 2/2</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>16</v>
+      </c>
+      <c r="D618" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E618" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F618" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G618" t="inlineStr"/>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H618"/>
+  <dimension ref="A1:H619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19184,6 +19184,36 @@
         </is>
       </c>
     </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Rošt lamelový, 80x200 cm, DOUBLE KLASIK NEW</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>DOUBLE-KLASIK-ROŠT</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>20</v>
+      </c>
+      <c r="D619" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E619" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F619" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G619" t="inlineStr"/>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H619"/>
+  <dimension ref="A1:H621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19214,6 +19214,66 @@
         </is>
       </c>
     </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120x200 masiv borovice - VMK12C</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>VMK-12C-120 1/2</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>20</v>
+      </c>
+      <c r="D620" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E620" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F620" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G620" t="inlineStr"/>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120x200 masiv borovice - VMK12C</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>VMK-12C-120 2/2</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>15</v>
+      </c>
+      <c r="D621" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E621" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F621" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G621" t="inlineStr"/>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H621"/>
+  <dimension ref="A1:H624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19274,6 +19274,96 @@
         </is>
       </c>
     </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MONA KIDBED TWO + rošty  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>MONA-KIDBED-TWO 1/3</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>25</v>
+      </c>
+      <c r="D622" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E622" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F622" t="n">
+        <v>1</v>
+      </c>
+      <c r="G622" t="inlineStr"/>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MONA KIDBED TWO + rošty  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>MONA-KIDBED-TWO 2/3</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>20</v>
+      </c>
+      <c r="D623" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E623" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F623" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G623" t="inlineStr"/>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MONA KIDBED TWO + rošty  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>MONA-KIDBED-TWO 3/3</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>24</v>
+      </c>
+      <c r="D624" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E624" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F624" t="n">
+        <v>1</v>
+      </c>
+      <c r="G624" t="inlineStr"/>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H624"/>
+  <dimension ref="A1:H626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19364,6 +19364,66 @@
         </is>
       </c>
     </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Dětská postel ALEXANDER PINE vč. roštu  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>ALEXANDER-PINE 1/2</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>21</v>
+      </c>
+      <c r="D625" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E625" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F625" t="n">
+        <v>1</v>
+      </c>
+      <c r="G625" t="inlineStr"/>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Dětská postel ALEXANDER PINE vč. roštu  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>ALEXANDER-PINE 2/2</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>30</v>
+      </c>
+      <c r="D626" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E626" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F626" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G626" t="inlineStr"/>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H626"/>
+  <dimension ref="A1:H627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19424,6 +19424,36 @@
         </is>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Pěnová matrace HELIOS pěna výška 20 cm</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>MAT-HELIOS</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>15</v>
+      </c>
+      <c r="D627" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E627" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F627" t="n">
+        <v>1</v>
+      </c>
+      <c r="G627" t="inlineStr"/>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H627"/>
+  <dimension ref="A1:H629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19454,6 +19454,66 @@
         </is>
       </c>
     </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 90x200 cm z masivní borovice VMK3B bezbarvý lak</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>VMK3B-90 1/2</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>12</v>
+      </c>
+      <c r="D628" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E628" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F628" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G628" t="inlineStr"/>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 90x200 cm z masivní borovice VMK3B bezbarvý lak</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>VMK3B-90 2/2</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>18</v>
+      </c>
+      <c r="D629" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E629" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F629" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G629" t="inlineStr"/>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H629"/>
+  <dimension ref="A1:H631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19514,6 +19514,66 @@
         </is>
       </c>
     </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 90x200 masiv borovice - VMK13B</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>VMK13B-90-1/3</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>12</v>
+      </c>
+      <c r="D630" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E630" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F630" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G630" t="inlineStr"/>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 90x200 masiv borovice - VMK13B</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>VMK13B-90-2/3</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>18</v>
+      </c>
+      <c r="D631" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E631" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F631" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G631" t="inlineStr"/>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H631"/>
+  <dimension ref="A1:H632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19574,6 +19574,36 @@
         </is>
       </c>
     </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Dětská matrace POLO HR 10 cm – HR studená pěna H2, pratelný potah Jersey</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>MAT-POLO</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>8</v>
+      </c>
+      <c r="D632" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E632" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F632" t="n">
+        <v>2</v>
+      </c>
+      <c r="G632" t="inlineStr"/>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H632"/>
+  <dimension ref="A1:H634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19604,6 +19604,66 @@
         </is>
       </c>
     </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Dětská postel ANNITTI PINE z masivu borovice se zábranou, roštem a zásuvkami</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>ANNITTI-PINE 1/2</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>21</v>
+      </c>
+      <c r="D633" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E633" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F633" t="n">
+        <v>1</v>
+      </c>
+      <c r="G633" t="inlineStr"/>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Dětská postel ANNITTI PINE z masivu borovice se zábranou, roštem a zásuvkami</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>ANNITTI-PINE 2/2</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>30</v>
+      </c>
+      <c r="D634" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E634" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F634" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G634" t="inlineStr"/>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H634"/>
+  <dimension ref="A1:H635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19664,6 +19664,36 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Sedací vak ELEFANT šedý</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>VAK-ELEFANT</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>5</v>
+      </c>
+      <c r="D635" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E635" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F635" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G635" t="inlineStr"/>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H635"/>
+  <dimension ref="A1:H638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19694,6 +19694,96 @@
         </is>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Patrová postel s přistýlkou PYKE KIDBED FOUR + rošty  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>PYKE-KIDBED-FOUR 1/3</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>32</v>
+      </c>
+      <c r="D636" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E636" t="n">
+        <v>1</v>
+      </c>
+      <c r="F636" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G636" t="inlineStr"/>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Patrová postel s přistýlkou PYKE KIDBED FOUR + rošty  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>PYKE-KIDBED-FOUR 2/3</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>37</v>
+      </c>
+      <c r="D637" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E637" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F637" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G637" t="inlineStr"/>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Patrová postel s přistýlkou PYKE KIDBED FOUR + rošty  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>PYKE-KIDBED-FOUR 3/3</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>24</v>
+      </c>
+      <c r="D638" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E638" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F638" t="n">
+        <v>1</v>
+      </c>
+      <c r="G638" t="inlineStr"/>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H638"/>
+  <dimension ref="A1:H639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19784,6 +19784,36 @@
         </is>
       </c>
     </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Matrace SVEA PUR 14 cm H3 – odolná pěnová matrace s pratelným potahem</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>MAT-SVEA</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>10</v>
+      </c>
+      <c r="D639" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E639" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F639" t="n">
+        <v>2</v>
+      </c>
+      <c r="G639" t="inlineStr"/>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H639"/>
+  <dimension ref="A1:H640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19814,6 +19814,36 @@
         </is>
       </c>
     </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Prostěradlo Froté 90 x 200 cm</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>PROSTĚRADLO</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>2</v>
+      </c>
+      <c r="D640" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E640" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F640" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G640" t="inlineStr"/>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H640"/>
+  <dimension ref="A1:H641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19844,6 +19844,36 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Dětská matrace JUNIOR COCO 11 cm – PUR pěna T25 + kokosová vrstva, H3</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>MAT-JUNIOR-COCO</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>8</v>
+      </c>
+      <c r="D641" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E641" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F641" t="n">
+        <v>2</v>
+      </c>
+      <c r="G641" t="inlineStr"/>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H641"/>
+  <dimension ref="A1:H643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19874,6 +19874,66 @@
         </is>
       </c>
     </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Patrová postel TEEMO KIDBED FIVE + rošt</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>TEEMO-KIDBED-FIVE 1/2</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>22</v>
+      </c>
+      <c r="D642" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E642" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F642" t="n">
+        <v>1</v>
+      </c>
+      <c r="G642" t="inlineStr"/>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Patrová postel TEEMO KIDBED FIVE + rošt</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>TEEMO-KIDBED-FIVE 2/2</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>33</v>
+      </c>
+      <c r="D643" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E643" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F643" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G643" t="inlineStr"/>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H643"/>
+  <dimension ref="A1:H644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19934,6 +19934,36 @@
         </is>
       </c>
     </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Pěnová matrace SVEA PUR Aloe Vera 14 cm – PUR pěna T25, H3, pratelný potah, nosnost 80 kg</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>MAT-SVEA</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>8</v>
+      </c>
+      <c r="D644" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E644" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F644" t="n">
+        <v>2</v>
+      </c>
+      <c r="G644" t="inlineStr"/>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H644"/>
+  <dimension ref="A1:H647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19964,6 +19964,96 @@
         </is>
       </c>
     </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Patrová postel BRUNO PINE vč. roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>BRUNO-PINE 1/3</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>30</v>
+      </c>
+      <c r="D645" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E645" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F645" t="n">
+        <v>1</v>
+      </c>
+      <c r="G645" t="inlineStr"/>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Patrová postel BRUNO PINE vč. roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>BRUNO-PINE 2/3</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>27</v>
+      </c>
+      <c r="D646" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E646" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F646" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G646" t="inlineStr"/>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Patrová postel BRUNO PINE vč. roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>BRUNO-PINE 3/3</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>24</v>
+      </c>
+      <c r="D647" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E647" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F647" t="n">
+        <v>1</v>
+      </c>
+      <c r="G647" t="inlineStr"/>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H647"/>
+  <dimension ref="A1:H648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20054,6 +20054,36 @@
         </is>
       </c>
     </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Pěnová matrace s kokosovou vrstvou 15 cm ADULT COCO Aloe Vera | PUR pěna T25 H3</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>MAT-ADULT-COCO</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>10</v>
+      </c>
+      <c r="D648" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E648" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F648" t="n">
+        <v>2</v>
+      </c>
+      <c r="G648" t="inlineStr"/>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H648"/>
+  <dimension ref="A1:H650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20084,6 +20084,66 @@
         </is>
       </c>
     </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120x200 masiv borovice - VMK11D</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>VMK11D-120 1/2</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>20</v>
+      </c>
+      <c r="D649" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E649" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F649" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G649" t="inlineStr"/>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120x200 masiv borovice - VMK11D</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>VMK11D-120 2/2</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>15</v>
+      </c>
+      <c r="D650" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E650" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F650" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G650" t="inlineStr"/>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H650"/>
+  <dimension ref="A1:H652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20144,6 +20144,66 @@
         </is>
       </c>
     </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Dětská postel NIKY KIDBED ONE ze dřeva + rošt  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>NIKY-KIDBED-ONE 1/2</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>21</v>
+      </c>
+      <c r="D651" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E651" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F651" t="n">
+        <v>1</v>
+      </c>
+      <c r="G651" t="inlineStr"/>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Dětská postel NIKY KIDBED ONE ze dřeva + rošt  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>NIKY-KIDBED-ONE 2/2</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>30</v>
+      </c>
+      <c r="D652" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E652" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F652" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G652" t="inlineStr"/>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H652"/>
+  <dimension ref="A1:H654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20204,6 +20204,66 @@
         </is>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 90x200 cm z masivní borovice VMK1B s roštem</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>VMK1B-90 1/2</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>18</v>
+      </c>
+      <c r="D653" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E653" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F653" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G653" t="inlineStr"/>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 90x200 cm z masivní borovice VMK1B s roštem</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>VMK1B-90 2/2</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>12</v>
+      </c>
+      <c r="D654" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E654" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F654" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G654" t="inlineStr"/>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H654"/>
+  <dimension ref="A1:H655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20264,6 +20264,36 @@
         </is>
       </c>
     </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Zásuvka pod postel LK150 z masivní borovice – 97 × 85 cm</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>VMK1B-90</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>8</v>
+      </c>
+      <c r="D655" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E655" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F655" t="n">
+        <v>1</v>
+      </c>
+      <c r="G655" t="inlineStr"/>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -20272,7 +20272,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>VMK1B-90</t>
+          <t>ZÁSUVKA-LK150-97</t>
         </is>
       </c>
       <c r="C655" t="n">

--- a/products.xlsx
+++ b/products.xlsx
@@ -17950,7 +17950,7 @@
       <c r="G577" t="inlineStr"/>
       <c r="H577" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -16300,7 +16300,7 @@
       <c r="G522" t="inlineStr"/>
       <c r="H522" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -10390,7 +10390,7 @@
       <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -7540,7 +7540,7 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7600,7 @@
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H655"/>
+  <dimension ref="A1:H657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20294,6 +20294,66 @@
         </is>
       </c>
     </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120x200 cm z masivní borovice VMK1B s roštem</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>VMK 1B - 120 1/2</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>18</v>
+      </c>
+      <c r="D656" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E656" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F656" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G656" t="inlineStr"/>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120x200 cm z masivní borovice VMK1B s roštem</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>VMK 1B - 120 2/2</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>12</v>
+      </c>
+      <c r="D657" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E657" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F657" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G657" t="inlineStr"/>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H657"/>
+  <dimension ref="A1:H659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20354,6 +20354,66 @@
         </is>
       </c>
     </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120x200 masiv borovice - VMK10D</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>VMK 10D - 120 1/2</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>18</v>
+      </c>
+      <c r="D658" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E658" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F658" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G658" t="inlineStr"/>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120x200 masiv borovice - VMK10D</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>VMK 10D - 120 2/2</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>12</v>
+      </c>
+      <c r="D659" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E659" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F659" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G659" t="inlineStr"/>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H659"/>
+  <dimension ref="A1:H661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20414,6 +20414,66 @@
         </is>
       </c>
     </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120×200 cm z masivu borovice s roštem – VMK2B moření dub</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>VMK 2B - 120 1/2</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>18</v>
+      </c>
+      <c r="D660" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E660" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F660" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G660" t="inlineStr"/>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120×200 cm z masivu borovice s roštem – VMK2B moření dub</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>VMK 2B - 120 2/2</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>12</v>
+      </c>
+      <c r="D661" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E661" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F661" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G661" t="inlineStr"/>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H661"/>
+  <dimension ref="A1:H663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20474,6 +20474,66 @@
         </is>
       </c>
     </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 140x200 masiv borovice - VMK12B</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>VMK 12B - 140 1/2</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>20</v>
+      </c>
+      <c r="D662" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E662" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F662" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G662" t="inlineStr"/>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 140x200 masiv borovice - VMK12B</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>VMK 12B - 140 2/2</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>14</v>
+      </c>
+      <c r="D663" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E663" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F663" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G663" t="inlineStr"/>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H663"/>
+  <dimension ref="A1:H665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20534,6 +20534,66 @@
         </is>
       </c>
     </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120x200 cm z masivu borovice VMK3B barva bílá</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>VMK 3B - 120 1/2</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>18</v>
+      </c>
+      <c r="D664" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E664" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F664" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G664" t="inlineStr"/>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120x200 cm z masivu borovice VMK3B barva bílá</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>VMK 3B - 120 2/2</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>12</v>
+      </c>
+      <c r="D665" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E665" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F665" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G665" t="inlineStr"/>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H665"/>
+  <dimension ref="A1:H667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20594,6 +20594,66 @@
         </is>
       </c>
     </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 180x200 masiv borovice - VMK9B</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>VMK 9B - 180 1/2</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>22</v>
+      </c>
+      <c r="D666" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E666" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F666" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G666" t="inlineStr"/>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 180x200 masiv borovice - VMK9B</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>VMK 9B - 180 2/2</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>16</v>
+      </c>
+      <c r="D667" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E667" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F667" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G667" t="inlineStr"/>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H667"/>
+  <dimension ref="A1:H669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20654,6 +20654,66 @@
         </is>
       </c>
     </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 90x200 cm z masivní borovice VMK1D s laťovým roštem</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>VMK 1D - 90 1/2</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>14</v>
+      </c>
+      <c r="D668" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E668" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F668" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G668" t="inlineStr"/>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 90x200 cm z masivní borovice VMK1D s laťovým roštem</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>VMK 1D - 90 2/2</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>10</v>
+      </c>
+      <c r="D669" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E669" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F669" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G669" t="inlineStr"/>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H669"/>
+  <dimension ref="A1:H671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20714,6 +20714,66 @@
         </is>
       </c>
     </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 90x200 cm z masivní borovice VMK5D s roštem</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>VMK 5D - 90 1/2</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>14</v>
+      </c>
+      <c r="D670" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E670" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F670" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G670" t="inlineStr"/>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 90x200 cm z masivní borovice VMK5D s roštem</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>VMK 5D - 90 2/2</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>10</v>
+      </c>
+      <c r="D671" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E671" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F671" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G671" t="inlineStr"/>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H671"/>
+  <dimension ref="A1:H673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20774,6 +20774,66 @@
         </is>
       </c>
     </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Postel BESKYD 80x200 cm z masivu borovice s laťovým roštem</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>BESKYD - 80 1/2</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>14</v>
+      </c>
+      <c r="D672" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E672" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F672" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G672" t="inlineStr"/>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Postel BESKYD 80x200 cm z masivu borovice s laťovým roštem</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>BESKYD - 80 2/2</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>10</v>
+      </c>
+      <c r="D673" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E673" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F673" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G673" t="inlineStr"/>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H673"/>
+  <dimension ref="A1:H675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20834,6 +20834,66 @@
         </is>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 200x200 masiv borovice - VMK8C</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>VMK 8C - 200 1/2</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>26</v>
+      </c>
+      <c r="D674" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E674" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F674" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G674" t="inlineStr"/>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 200x200 masiv borovice - VMK8C</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>VMK 8C - 200 2/2</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>18</v>
+      </c>
+      <c r="D675" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E675" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F675" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G675" t="inlineStr"/>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H675"/>
+  <dimension ref="A1:H677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20894,6 +20894,66 @@
         </is>
       </c>
     </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 140x200 cm BOSTON z masivu borovice včetně roštu</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>BOSTON - 140 1/2</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>26</v>
+      </c>
+      <c r="D676" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E676" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F676" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G676" t="inlineStr"/>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 140x200 cm BOSTON z masivu borovice včetně roštu</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>BOSTON - 140 2/2</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>12</v>
+      </c>
+      <c r="D677" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E677" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F677" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G677" t="inlineStr"/>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H677"/>
+  <dimension ref="A1:H680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20954,6 +20954,96 @@
         </is>
       </c>
     </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Postel 2S, 90x200, dub sonoma, NORTY TYP 28</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>NORTY TYP 28 1/3</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>40</v>
+      </c>
+      <c r="D678" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E678" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F678" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G678" t="inlineStr"/>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Postel 2S, 90x200, dub sonoma, NORTY TYP 28</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>NORTY TYP 28 2/3</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>15</v>
+      </c>
+      <c r="D679" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E679" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F679" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G679" t="inlineStr"/>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Postel 2S, 90x200, dub sonoma, NORTY TYP 28</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>NORTY TYP 28 3/3</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>38</v>
+      </c>
+      <c r="D680" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E680" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F680" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G680" t="inlineStr"/>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H680"/>
+  <dimension ref="A1:H681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21044,6 +21044,36 @@
         </is>
       </c>
     </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Zásuvka / šuplík pod postel LK152, 197 × 65 cm, masivní borovice</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>ZÁSUVKA LK152</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>20</v>
+      </c>
+      <c r="D681" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E681" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F681" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G681" t="inlineStr"/>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H681"/>
+  <dimension ref="A1:H684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21074,6 +21074,96 @@
         </is>
       </c>
     </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MONIKA PINE vč. roštů | 90 x 200 cm, barva modrá  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>MONIKA PINE 1/3</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>21</v>
+      </c>
+      <c r="D682" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E682" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F682" t="n">
+        <v>1</v>
+      </c>
+      <c r="G682" t="inlineStr"/>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MONIKA PINE vč. roštů | 90 x 200 cm, barva modrá  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>MONIKA PINE 2/3</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>20</v>
+      </c>
+      <c r="D683" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E683" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F683" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G683" t="inlineStr"/>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MONIKA PINE vč. roštů | 90 x 200 cm, barva modrá  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>MONIKA PINE 3/3</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>24</v>
+      </c>
+      <c r="D684" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E684" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F684" t="n">
+        <v>1</v>
+      </c>
+      <c r="G684" t="inlineStr"/>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H684"/>
+  <dimension ref="A1:H687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21164,6 +21164,96 @@
         </is>
       </c>
     </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MAREK PINE z masivu borovice 90x200 cm včetně roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>MAREK PINE 1/3</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>25</v>
+      </c>
+      <c r="D685" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E685" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F685" t="n">
+        <v>1</v>
+      </c>
+      <c r="G685" t="inlineStr"/>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MAREK PINE z masivu borovice 90x200 cm včetně roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>MAREK PINE 2/3</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>20</v>
+      </c>
+      <c r="D686" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E686" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F686" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G686" t="inlineStr"/>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MAREK PINE z masivu borovice 90x200 cm včetně roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>MAREK PINE 3/3</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>24</v>
+      </c>
+      <c r="D687" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E687" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F687" t="n">
+        <v>1</v>
+      </c>
+      <c r="G687" t="inlineStr"/>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H687"/>
+  <dimension ref="A1:H690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21254,6 +21254,96 @@
         </is>
       </c>
     </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Patrová postel JUNIOR PLUS 90×200 cm z masivní borovice pro děti a teenagery</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>MAREK PINE 1/3</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>25</v>
+      </c>
+      <c r="D688" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E688" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F688" t="n">
+        <v>1</v>
+      </c>
+      <c r="G688" t="inlineStr"/>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Patrová postel JUNIOR PLUS 90×200 cm z masivní borovice pro děti a teenagery</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>MAREK PINE 2/3</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>20</v>
+      </c>
+      <c r="D689" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E689" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F689" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G689" t="inlineStr"/>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Patrová postel JUNIOR PLUS 90×200 cm z masivní borovice pro děti a teenagery</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>MAREK PINE 3/3</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>15</v>
+      </c>
+      <c r="D690" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E690" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F690" t="n">
+        <v>1</v>
+      </c>
+      <c r="G690" t="inlineStr"/>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -21262,7 +21262,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>MAREK PINE 1/3</t>
+          <t>JUNIOR PLUS 1/3</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -21292,7 +21292,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>MAREK PINE 2/3</t>
+          <t>JUNIOR PLUS 2/3</t>
         </is>
       </c>
       <c r="C689" t="n">
@@ -21322,7 +21322,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>MAREK PINE 3/3</t>
+          <t>JUNIOR PLUS 3/3</t>
         </is>
       </c>
       <c r="C690" t="n">

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H690"/>
+  <dimension ref="A1:H691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21344,6 +21344,36 @@
         </is>
       </c>
     </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Zásuvka pod postel LK151, masivní borovice, 150 × 85 cm</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>ZÁSUVKA LK151</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>18</v>
+      </c>
+      <c r="D691" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E691" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F691" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G691" t="inlineStr"/>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H691"/>
+  <dimension ref="A1:H693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21374,6 +21374,66 @@
         </is>
       </c>
     </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Patrová postel KL-135</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>POSTEL KL-135 1/2</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>35</v>
+      </c>
+      <c r="D692" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E692" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F692" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G692" t="inlineStr"/>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Patrová postel KL-135</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>POSTEL KL-135 2/2</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>28</v>
+      </c>
+      <c r="D693" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E693" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F693" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G693" t="inlineStr"/>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H693"/>
+  <dimension ref="A1:H695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21434,6 +21434,66 @@
         </is>
       </c>
     </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Postel LENA 90x200 | MASIV BOROVICE</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>LENA-90X200 1/2</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>15</v>
+      </c>
+      <c r="D694" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E694" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F694" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G694" t="inlineStr"/>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Postel LENA 90x200 | MASIV BOROVICE</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>LENA-90X200 2/3</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>10</v>
+      </c>
+      <c r="D695" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E695" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F695" t="n">
+        <v>2</v>
+      </c>
+      <c r="G695" t="inlineStr"/>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H695"/>
+  <dimension ref="A1:H697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21494,6 +21494,66 @@
         </is>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Rohová jídelní lavice JENARAE</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>ROHOVÁ LAVICE JENARAE 1/2</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>32</v>
+      </c>
+      <c r="D696" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E696" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F696" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G696" t="inlineStr"/>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Rohová jídelní lavice JENARAE</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>ROHOVÁ LAVICE JENARAE 2/2</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>7</v>
+      </c>
+      <c r="D697" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E697" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F697" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G697" t="inlineStr"/>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H697"/>
+  <dimension ref="A1:H701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21554,6 +21554,126 @@
         </is>
       </c>
     </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Jídelní rohový set JOKULL dub kraft / koženka bílá</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>SET JOKULL 1/4</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>23</v>
+      </c>
+      <c r="D698" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E698" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F698" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G698" t="inlineStr"/>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Jídelní rohový set JOKULL dub kraft / koženka bílá</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>SET JOKULL 2/4</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>6</v>
+      </c>
+      <c r="D699" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E699" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F699" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G699" t="inlineStr"/>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Jídelní rohový set JOKULL dub kraft / koženka bílá</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>SET JOKULL 3/4</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>12</v>
+      </c>
+      <c r="D700" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E700" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F700" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G700" t="inlineStr"/>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Jídelní rohový set JOKULL dub kraft / koženka bílá</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>SET JOKULL 4/4</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>7</v>
+      </c>
+      <c r="D701" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E701" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F701" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G701" t="inlineStr"/>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H701"/>
+  <dimension ref="A1:H702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21674,6 +21674,36 @@
         </is>
       </c>
     </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Komoda LATHAM SX-03 nízká s posuvnými dvířky a policovým prostorem</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>KOMODA LATHAM SX-03</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>24</v>
+      </c>
+      <c r="D702" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E702" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F702" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G702" t="inlineStr"/>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H702"/>
+  <dimension ref="A1:H704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21704,6 +21704,66 @@
         </is>
       </c>
     </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 90x200 borovice VMK5C bezbarvý lak</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>VMK 5C - 90 1/2</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>18</v>
+      </c>
+      <c r="D703" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E703" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F703" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G703" t="inlineStr"/>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 90x200 borovice VMK5C bezbarvý lak</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>VMK 5C - 90 2/2</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>10</v>
+      </c>
+      <c r="D704" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E704" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F704" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G704" t="inlineStr"/>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H704"/>
+  <dimension ref="A1:H706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21764,6 +21764,66 @@
         </is>
       </c>
     </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120×200 cm z masivu borovice s roštem – VMK2B bezbarvý lak</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>VMK 2B - 120 1/2</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>20</v>
+      </c>
+      <c r="D705" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E705" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F705" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G705" t="inlineStr"/>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 120×200 cm z masivu borovice s roštem – VMK2B bezbarvý lak</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>VMK 2B - 120 2/2</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>12</v>
+      </c>
+      <c r="D706" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E706" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F706" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G706" t="inlineStr"/>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H706"/>
+  <dimension ref="A1:H707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21824,6 +21824,36 @@
         </is>
       </c>
     </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Konferenční stolek rozkládací BASILE</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>stolek BASILE</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>16</v>
+      </c>
+      <c r="D707" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E707" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F707" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G707" t="inlineStr"/>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H707"/>
+  <dimension ref="A1:H708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21854,6 +21854,36 @@
         </is>
       </c>
     </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Regál LATHAM-06 policový s dvířky a zásuvkami</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>regál LATHAM-06</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>37</v>
+      </c>
+      <c r="D708" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E708" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F708" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G708" t="inlineStr"/>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H708"/>
+  <dimension ref="A1:H709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21884,6 +21884,36 @@
         </is>
       </c>
     </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Závěsná police MX-13</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>regál LATHAM-06</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>8</v>
+      </c>
+      <c r="D709" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E709" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F709" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G709" t="inlineStr"/>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H709"/>
+  <dimension ref="A1:H710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21914,6 +21914,36 @@
         </is>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Sedací botník DEYLIS se sedákem, policemi na boty a úložným prostorem do předsíně</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>botník DEYLIS</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>26</v>
+      </c>
+      <c r="D710" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E710" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F710" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G710" t="inlineStr"/>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H710"/>
+  <dimension ref="A1:H712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21944,6 +21944,66 @@
         </is>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Komoda-8 BLAISE NEW</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>komoda-8 BLAISE NEW 1/2</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>27</v>
+      </c>
+      <c r="D711" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E711" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F711" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G711" t="inlineStr"/>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Komoda-8 BLAISE NEW</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>komoda-8 BLAISE NEW 2/2</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>29</v>
+      </c>
+      <c r="D712" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E712" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F712" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G712" t="inlineStr"/>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H712"/>
+  <dimension ref="A1:H713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22004,6 +22004,36 @@
         </is>
       </c>
     </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Televizní stolek DELVIN</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>stolek DELVIN</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>32</v>
+      </c>
+      <c r="D713" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E713" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F713" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G713" t="inlineStr"/>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H713"/>
+  <dimension ref="A1:H714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22034,6 +22034,36 @@
         </is>
       </c>
     </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Jídelní stůl SN-04 80 × 60 cm – kompaktní stůl do kuchyně a jídelny</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>stůl SN-04</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>12</v>
+      </c>
+      <c r="D714" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E714" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F714" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G714" t="inlineStr"/>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H714"/>
+  <dimension ref="A1:H715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22064,6 +22064,36 @@
         </is>
       </c>
     </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Televizní stolek DOMINIC 92 × 52 × 62 cm – moderní TV stolek s úložným prostorem</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>stolek DOMINIC</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>25</v>
+      </c>
+      <c r="D715" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E715" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F715" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G715" t="inlineStr"/>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H715"/>
+  <dimension ref="A1:H716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22094,6 +22094,36 @@
         </is>
       </c>
     </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Rohová jídelní lavice HAROLD s úložným prostorem 150 × 110 cm – univerzální pravá/levá varianta</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>lavice HAROLD</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>42</v>
+      </c>
+      <c r="D716" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E716" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F716" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G716" t="inlineStr"/>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H716"/>
+  <dimension ref="A1:H720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22124,6 +22124,126 @@
         </is>
       </c>
     </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Jídelní rohový set JENARAE dub tacho - koženka hnědá</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>rohový set JANARAE 1/4</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>32</v>
+      </c>
+      <c r="D717" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E717" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F717" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G717" t="inlineStr"/>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Jídelní rohový set JENARAE dub tacho - koženka hnědá</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>rohový set JANARAE 2/4</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>7</v>
+      </c>
+      <c r="D718" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E718" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F718" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Jídelní rohový set JENARAE dub tacho - koženka hnědá</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>rohový set JANARAE 3/4</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>21</v>
+      </c>
+      <c r="D719" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E719" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F719" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G719" t="inlineStr"/>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Jídelní rohový set JENARAE dub tacho - koženka hnědá</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>rohový set JANARAE 4/4</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>8</v>
+      </c>
+      <c r="D720" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E720" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F720" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G720" t="inlineStr"/>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H720"/>
+  <dimension ref="A1:H721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22244,6 +22244,36 @@
         </is>
       </c>
     </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Jídelní židle ARIANNA šedá – čalouněná jídelní židle s ocelovou konstrukcí</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>židle ARIANNA</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>8</v>
+      </c>
+      <c r="D721" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E721" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F721" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G721" t="inlineStr"/>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H721"/>
+  <dimension ref="A1:H722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22274,6 +22274,36 @@
         </is>
       </c>
     </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Noční stolek BOGAN NEW 1S bílý</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>NČ BOGAN NEW</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>11</v>
+      </c>
+      <c r="D722" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E722" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F722" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G722" t="inlineStr"/>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8380,7 +8380,7 @@
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -6880,7 +6880,7 @@
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -11020,7 +11020,7 @@
       <c r="G346" t="inlineStr"/>
       <c r="H346" t="inlineStr">
         <is>
-          <t>TOPTRANS</t>
+          <t>ALL</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H722"/>
+  <dimension ref="A1:H724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22304,6 +22304,66 @@
         </is>
       </c>
     </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Televizní stolek DOMINIC</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>stolek DOMINIC 1/2</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>25</v>
+      </c>
+      <c r="D723" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E723" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F723" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G723" t="inlineStr"/>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Televizní stolek DOMINIC</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>stolek DOMINIC 2/2</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>10</v>
+      </c>
+      <c r="D724" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E724" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F724" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G724" t="inlineStr"/>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H724"/>
+  <dimension ref="A1:H725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22364,6 +22364,36 @@
         </is>
       </c>
     </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Výklopný botník MARCOS se zásuvkou a regálem – úzký dvouřadý botník do předsíně 80 × 117 × 25 cm</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>botník MARCOS</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>31</v>
+      </c>
+      <c r="D725" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E725" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F725" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G725" t="inlineStr"/>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H725"/>
+  <dimension ref="A1:H726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22394,6 +22394,36 @@
         </is>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Botník KENDALL 80 cm – policový regál na boty do předsíně, 80 × 68 × 27 cm</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>botník KENDALL</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>16</v>
+      </c>
+      <c r="D726" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E726" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F726" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G726" t="inlineStr"/>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H726"/>
+  <dimension ref="A1:H728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22424,6 +22424,66 @@
         </is>
       </c>
     </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 160x200 cm z masivní borovice VMK3B barva bílá</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>VMK 3B - 160 1/2</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>22</v>
+      </c>
+      <c r="D727" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E727" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F727" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G727" t="inlineStr"/>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Dřevěná postel 160x200 cm z masivní borovice VMK3B barva bílá</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>VMK 3B - 160 2/2</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>16</v>
+      </c>
+      <c r="D728" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E728" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F728" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G728" t="inlineStr"/>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H728"/>
+  <dimension ref="A1:H729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22484,6 +22484,36 @@
         </is>
       </c>
     </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Rozkládací pohovka ALISIA šedohnědá Taupe / gold chrom zlatý</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>pohovka ALISIA</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>34</v>
+      </c>
+      <c r="D729" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E729" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F729" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G729" t="inlineStr"/>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H729"/>
+  <dimension ref="A1:H731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22514,6 +22514,66 @@
         </is>
       </c>
     </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Policový botník MARC dub sonoma – vysoký úzký regál na boty s otevřenými policemi 180 cm</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>botník MARC 1/2</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>15</v>
+      </c>
+      <c r="D730" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E730" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F730" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G730" t="inlineStr"/>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Policový botník MARC dub sonoma – vysoký úzký regál na boty s otevřenými policemi 180 cm</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>botník MARC 2/2</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>24</v>
+      </c>
+      <c r="D731" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E731" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F731" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G731" t="inlineStr"/>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H731"/>
+  <dimension ref="A1:H732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22574,6 +22574,36 @@
         </is>
       </c>
     </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Nástavec na skříň šíře 90 cm INVITA TYP 9 bílý</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>nástavec INVITA TYP 9</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>22</v>
+      </c>
+      <c r="D732" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E732" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F732" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G732" t="inlineStr"/>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H732"/>
+  <dimension ref="A1:H736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22604,6 +22604,126 @@
         </is>
       </c>
     </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Patrová postel RUDI PINE vč. roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>RUDI PINE 1/4</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>27</v>
+      </c>
+      <c r="D733" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E733" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F733" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G733" t="inlineStr"/>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Patrová postel RUDI PINE vč. roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>RUDI PINE 2/4</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>19</v>
+      </c>
+      <c r="D734" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E734" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F734" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G734" t="inlineStr"/>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Patrová postel RUDI PINE vč. roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>RUDI PINE 3/4</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>31</v>
+      </c>
+      <c r="D735" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E735" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F735" t="n">
+        <v>1</v>
+      </c>
+      <c r="G735" t="inlineStr"/>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Patrová postel RUDI PINE vč. roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>RUDI PINE 4/4</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>5</v>
+      </c>
+      <c r="D736" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E736" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F736" t="n">
+        <v>1</v>
+      </c>
+      <c r="G736" t="inlineStr"/>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>NOVAPOST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
